--- a/data/MedTech_YTD_Standardized.xlsx
+++ b/data/MedTech_YTD_Standardized.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beacononehcp-my.sharepoint.com/personal/hannah_peric_beacononehcp_com/Documents/Documents/medtech-dashboard/Medtech-Dashboard-M-A/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87401E5D-D625-421A-9108-DB97AEC9136C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="878">
   <si>
     <t>Company</t>
   </si>
@@ -2652,6 +2652,9 @@
   </si>
   <si>
     <t>Q2 2025</t>
+  </si>
+  <si>
+    <t>Pixyl and Caerus Medical</t>
   </si>
 </sst>
 </file>
@@ -4790,7 +4793,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>261</v>
+        <v>877</v>
       </c>
       <c r="B76" t="s">
         <v>261</v>

--- a/data/MedTech_YTD_Standardized.xlsx
+++ b/data/MedTech_YTD_Standardized.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beacononehcp-my.sharepoint.com/personal/hannah_peric_beacononehcp_com/Documents/Documents/medtech-dashboard/Medtech-Dashboard-M-A/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87401E5D-D625-421A-9108-DB97AEC9136C}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A90AD0A0-6616-4481-9D50-C068C173AF33}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1839" uniqueCount="875">
   <si>
     <t>Company</t>
   </si>
@@ -692,9 +692,6 @@
     <t>$497,000,000</t>
   </si>
   <si>
-    <t>OrganiX</t>
-  </si>
-  <si>
     <t>Terumo</t>
   </si>
   <si>
@@ -950,9 +947,6 @@
     <t>OrganOx</t>
   </si>
   <si>
-    <t>metra automated device for liver preservation up to 24 hours.</t>
-  </si>
-  <si>
     <t>Hudson Technologies</t>
   </si>
   <si>
@@ -2634,9 +2628,6 @@
   </si>
   <si>
     <t>$18300000000</t>
-  </si>
-  <si>
-    <t>$1500000000</t>
   </si>
   <si>
     <t>$815000000</t>
@@ -2724,7 +2715,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2741,8 +2732,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3056,7 +3046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" bestFit="1" customWidth="1"/>
@@ -3106,7 +3096,7 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -3129,7 +3119,7 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -3152,7 +3142,7 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
@@ -3175,7 +3165,7 @@
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -3198,7 +3188,7 @@
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
@@ -3221,7 +3211,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -3244,7 +3234,7 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -3267,7 +3257,7 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -3290,7 +3280,7 @@
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G10" t="s">
         <v>12</v>
@@ -3313,7 +3303,7 @@
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G11" t="s">
         <v>12</v>
@@ -3336,7 +3326,7 @@
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
@@ -3359,7 +3349,7 @@
         <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -3382,7 +3372,7 @@
         <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -3405,7 +3395,7 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G15" t="s">
         <v>12</v>
@@ -3428,7 +3418,7 @@
         <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
@@ -3451,7 +3441,7 @@
         <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G17" t="s">
         <v>59</v>
@@ -3474,7 +3464,7 @@
         <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G18" t="s">
         <v>59</v>
@@ -3497,7 +3487,7 @@
         <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G19" t="s">
         <v>59</v>
@@ -3520,7 +3510,7 @@
         <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G20" t="s">
         <v>59</v>
@@ -3543,7 +3533,7 @@
         <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G21" t="s">
         <v>59</v>
@@ -3566,7 +3556,7 @@
         <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G22" t="s">
         <v>59</v>
@@ -3589,7 +3579,7 @@
         <v>79</v>
       </c>
       <c r="F23" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G23" t="s">
         <v>59</v>
@@ -3612,7 +3602,7 @@
         <v>83</v>
       </c>
       <c r="F24" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G24" t="s">
         <v>59</v>
@@ -3635,7 +3625,7 @@
         <v>16</v>
       </c>
       <c r="F25" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G25" t="s">
         <v>59</v>
@@ -3658,7 +3648,7 @@
         <v>90</v>
       </c>
       <c r="F26" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G26" t="s">
         <v>91</v>
@@ -3681,7 +3671,7 @@
         <v>16</v>
       </c>
       <c r="F27" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G27" t="s">
         <v>91</v>
@@ -3704,7 +3694,7 @@
         <v>98</v>
       </c>
       <c r="F28" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G28" t="s">
         <v>91</v>
@@ -3727,7 +3717,7 @@
         <v>16</v>
       </c>
       <c r="F29" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G29" t="s">
         <v>91</v>
@@ -3750,7 +3740,7 @@
         <v>16</v>
       </c>
       <c r="F30" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G30" t="s">
         <v>91</v>
@@ -3773,7 +3763,7 @@
         <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G31" t="s">
         <v>91</v>
@@ -3796,7 +3786,7 @@
         <v>111</v>
       </c>
       <c r="F32" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G32" t="s">
         <v>91</v>
@@ -3819,7 +3809,7 @@
         <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G33" t="s">
         <v>91</v>
@@ -3842,7 +3832,7 @@
         <v>119</v>
       </c>
       <c r="F34" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G34" t="s">
         <v>91</v>
@@ -3865,7 +3855,7 @@
         <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G35" t="s">
         <v>123</v>
@@ -3888,7 +3878,7 @@
         <v>127</v>
       </c>
       <c r="F36" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G36" t="s">
         <v>123</v>
@@ -3911,7 +3901,7 @@
         <v>130</v>
       </c>
       <c r="F37" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G37" t="s">
         <v>123</v>
@@ -3934,7 +3924,7 @@
         <v>134</v>
       </c>
       <c r="F38" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G38" t="s">
         <v>123</v>
@@ -3957,7 +3947,7 @@
         <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G39" t="s">
         <v>123</v>
@@ -3980,7 +3970,7 @@
         <v>16</v>
       </c>
       <c r="F40" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G40" t="s">
         <v>123</v>
@@ -4003,7 +3993,7 @@
         <v>16</v>
       </c>
       <c r="F41" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G41" t="s">
         <v>123</v>
@@ -4026,7 +4016,7 @@
         <v>148</v>
       </c>
       <c r="F42" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G42" t="s">
         <v>123</v>
@@ -4049,7 +4039,7 @@
         <v>152</v>
       </c>
       <c r="F43" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G43" t="s">
         <v>123</v>
@@ -4072,7 +4062,7 @@
         <v>156</v>
       </c>
       <c r="F44" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G44" t="s">
         <v>123</v>
@@ -4095,7 +4085,7 @@
         <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G45" t="s">
         <v>123</v>
@@ -4118,7 +4108,7 @@
         <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G46" t="s">
         <v>163</v>
@@ -4141,7 +4131,7 @@
         <v>167</v>
       </c>
       <c r="F47" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G47" t="s">
         <v>163</v>
@@ -4164,7 +4154,7 @@
         <v>171</v>
       </c>
       <c r="F48" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G48" t="s">
         <v>163</v>
@@ -4187,7 +4177,7 @@
         <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G49" t="s">
         <v>163</v>
@@ -4210,7 +4200,7 @@
         <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G50" t="s">
         <v>163</v>
@@ -4233,7 +4223,7 @@
         <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G51" t="s">
         <v>163</v>
@@ -4256,7 +4246,7 @@
         <v>183</v>
       </c>
       <c r="F52" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G52" t="s">
         <v>163</v>
@@ -4279,7 +4269,7 @@
         <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G53" t="s">
         <v>163</v>
@@ -4302,7 +4292,7 @@
         <v>190</v>
       </c>
       <c r="F54" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G54" t="s">
         <v>163</v>
@@ -4325,7 +4315,7 @@
         <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G55" t="s">
         <v>163</v>
@@ -4348,7 +4338,7 @@
         <v>16</v>
       </c>
       <c r="F56" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G56" t="s">
         <v>163</v>
@@ -4371,7 +4361,7 @@
         <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G57" t="s">
         <v>200</v>
@@ -4394,7 +4384,7 @@
         <v>16</v>
       </c>
       <c r="F58" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G58" t="s">
         <v>200</v>
@@ -4417,7 +4407,7 @@
         <v>207</v>
       </c>
       <c r="F59" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G59" t="s">
         <v>200</v>
@@ -4440,7 +4430,7 @@
         <v>210</v>
       </c>
       <c r="F60" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G60" t="s">
         <v>211</v>
@@ -4463,7 +4453,7 @@
         <v>16</v>
       </c>
       <c r="F61" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G61" t="s">
         <v>215</v>
@@ -4486,7 +4476,7 @@
         <v>218</v>
       </c>
       <c r="F62" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G62" t="s">
         <v>215</v>
@@ -4509,7 +4499,7 @@
         <v>222</v>
       </c>
       <c r="F63" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G63" t="s">
         <v>215</v>
@@ -4517,22 +4507,22 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>307</v>
+      </c>
+      <c r="B64" t="s">
         <v>223</v>
-      </c>
-      <c r="B64" t="s">
-        <v>224</v>
       </c>
       <c r="C64" t="s">
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>224</v>
+      </c>
+      <c r="E64" t="s">
         <v>225</v>
       </c>
-      <c r="E64" t="s">
-        <v>226</v>
-      </c>
       <c r="F64" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G64" t="s">
         <v>215</v>
@@ -4540,7 +4530,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B65" t="s">
         <v>109</v>
@@ -4549,13 +4539,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E65" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F65" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G65" t="s">
         <v>215</v>
@@ -4563,7 +4553,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B66" t="s">
         <v>146</v>
@@ -4572,59 +4562,59 @@
         <v>9</v>
       </c>
       <c r="D66" t="s">
+        <v>229</v>
+      </c>
+      <c r="E66" t="s">
         <v>230</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
+        <v>277</v>
+      </c>
+      <c r="G66" t="s">
         <v>231</v>
-      </c>
-      <c r="F66" t="s">
-        <v>278</v>
-      </c>
-      <c r="G66" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>232</v>
+      </c>
+      <c r="B67" t="s">
         <v>233</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>234</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>235</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>236</v>
       </c>
-      <c r="E67" t="s">
-        <v>237</v>
-      </c>
       <c r="F67" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>237</v>
+      </c>
+      <c r="B68" t="s">
         <v>238</v>
-      </c>
-      <c r="B68" t="s">
-        <v>239</v>
       </c>
       <c r="C68" t="s">
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>239</v>
+      </c>
+      <c r="E68" t="s">
         <v>240</v>
       </c>
-      <c r="E68" t="s">
-        <v>241</v>
-      </c>
       <c r="F68" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G68" t="s">
         <v>215</v>
@@ -4632,45 +4622,45 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>241</v>
+      </c>
+      <c r="B69" t="s">
         <v>242</v>
-      </c>
-      <c r="B69" t="s">
-        <v>243</v>
       </c>
       <c r="C69" t="s">
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E69" t="s">
         <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G69" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>244</v>
+      </c>
+      <c r="B70" t="s">
         <v>245</v>
-      </c>
-      <c r="B70" t="s">
-        <v>246</v>
       </c>
       <c r="C70" t="s">
         <v>9</v>
       </c>
       <c r="D70" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E70" t="s">
         <v>16</v>
       </c>
       <c r="F70" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G70" t="s">
         <v>215</v>
@@ -4678,22 +4668,22 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>247</v>
+      </c>
+      <c r="B71" t="s">
         <v>248</v>
-      </c>
-      <c r="B71" t="s">
-        <v>249</v>
       </c>
       <c r="C71" t="s">
         <v>117</v>
       </c>
       <c r="D71" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E71" t="s">
         <v>16</v>
       </c>
       <c r="F71" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G71" t="s">
         <v>200</v>
@@ -4701,22 +4691,22 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B72" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C72" t="s">
         <v>117</v>
       </c>
       <c r="D72" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E72" t="s">
         <v>16</v>
       </c>
       <c r="F72" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G72" t="s">
         <v>200</v>
@@ -4724,22 +4714,22 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>251</v>
+      </c>
+      <c r="B73" t="s">
         <v>252</v>
-      </c>
-      <c r="B73" t="s">
-        <v>253</v>
       </c>
       <c r="C73" t="s">
         <v>9</v>
       </c>
       <c r="D73" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E73" t="s">
         <v>16</v>
       </c>
       <c r="F73" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G73" t="s">
         <v>200</v>
@@ -4747,22 +4737,22 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>254</v>
+      </c>
+      <c r="B74" t="s">
         <v>255</v>
-      </c>
-      <c r="B74" t="s">
-        <v>256</v>
       </c>
       <c r="C74" t="s">
         <v>9</v>
       </c>
       <c r="D74" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E74" t="s">
         <v>16</v>
       </c>
       <c r="F74" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G74" t="s">
         <v>91</v>
@@ -4770,22 +4760,22 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>257</v>
+      </c>
+      <c r="B75" t="s">
         <v>258</v>
-      </c>
-      <c r="B75" t="s">
-        <v>259</v>
       </c>
       <c r="C75" t="s">
         <v>9</v>
       </c>
       <c r="D75" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E75" t="s">
         <v>16</v>
       </c>
       <c r="F75" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G75" t="s">
         <v>91</v>
@@ -4793,669 +4783,646 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="B76" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C76" t="s">
         <v>9</v>
       </c>
       <c r="D76" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E76" t="s">
         <v>16</v>
       </c>
       <c r="F76" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G76" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
+      <c r="A77" t="s">
         <v>8</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" t="s">
+        <v>262</v>
+      </c>
+      <c r="C77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" t="s">
         <v>263</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="E77" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="F77" t="s">
+        <v>264</v>
+      </c>
+      <c r="G77" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>265</v>
+      </c>
+      <c r="B78" t="s">
+        <v>266</v>
+      </c>
+      <c r="C78" t="s">
         <v>9</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D78" t="s">
+        <v>267</v>
+      </c>
+      <c r="E78" t="s">
+        <v>16</v>
+      </c>
+      <c r="F78" t="s">
         <v>264</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="G78" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>268</v>
+      </c>
+      <c r="B79" t="s">
+        <v>269</v>
+      </c>
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" t="s">
+        <v>270</v>
+      </c>
+      <c r="E79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79" t="s">
+        <v>264</v>
+      </c>
+      <c r="G79" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>271</v>
+      </c>
+      <c r="B80" t="s">
+        <v>272</v>
+      </c>
+      <c r="C80" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" t="s">
+        <v>273</v>
+      </c>
+      <c r="E80" t="s">
+        <v>16</v>
+      </c>
+      <c r="F80" t="s">
+        <v>264</v>
+      </c>
+      <c r="G80" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>274</v>
+      </c>
+      <c r="B81" t="s">
+        <v>275</v>
+      </c>
+      <c r="C81" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" t="s">
+        <v>276</v>
+      </c>
+      <c r="E81" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" t="s">
+        <v>277</v>
+      </c>
+      <c r="G81" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>278</v>
+      </c>
+      <c r="B82" t="s">
+        <v>178</v>
+      </c>
+      <c r="C82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" t="s">
+        <v>279</v>
+      </c>
+      <c r="E82" t="s">
+        <v>16</v>
+      </c>
+      <c r="F82" t="s">
+        <v>277</v>
+      </c>
+      <c r="G82" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>280</v>
+      </c>
+      <c r="B83" t="s">
+        <v>281</v>
+      </c>
+      <c r="C83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" t="s">
+        <v>282</v>
+      </c>
+      <c r="E83" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" t="s">
+        <v>277</v>
+      </c>
+      <c r="G83" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>283</v>
+      </c>
+      <c r="B84" t="s">
+        <v>284</v>
+      </c>
+      <c r="C84" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" t="s">
+        <v>285</v>
+      </c>
+      <c r="E84" t="s">
+        <v>16</v>
+      </c>
+      <c r="F84" t="s">
+        <v>277</v>
+      </c>
+      <c r="G84" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>286</v>
+      </c>
+      <c r="B85" t="s">
+        <v>287</v>
+      </c>
+      <c r="C85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" t="s">
+        <v>288</v>
+      </c>
+      <c r="E85" t="s">
+        <v>16</v>
+      </c>
+      <c r="F85" t="s">
+        <v>277</v>
+      </c>
+      <c r="G85" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>289</v>
+      </c>
+      <c r="B86" t="s">
+        <v>290</v>
+      </c>
+      <c r="C86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86" t="s">
+        <v>291</v>
+      </c>
+      <c r="E86" t="s">
+        <v>16</v>
+      </c>
+      <c r="F86" t="s">
+        <v>277</v>
+      </c>
+      <c r="G86" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>292</v>
+      </c>
+      <c r="B87" t="s">
+        <v>293</v>
+      </c>
+      <c r="C87" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" t="s">
+        <v>294</v>
+      </c>
+      <c r="E87" t="s">
+        <v>16</v>
+      </c>
+      <c r="F87" t="s">
+        <v>277</v>
+      </c>
+      <c r="G87" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>295</v>
+      </c>
+      <c r="B88" t="s">
+        <v>88</v>
+      </c>
+      <c r="C88" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" t="s">
+        <v>296</v>
+      </c>
+      <c r="E88" t="s">
+        <v>297</v>
+      </c>
+      <c r="F88" t="s">
+        <v>277</v>
+      </c>
+      <c r="G88" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>298</v>
+      </c>
+      <c r="B89" t="s">
+        <v>299</v>
+      </c>
+      <c r="C89" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" t="s">
+        <v>300</v>
+      </c>
+      <c r="E89" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" t="s">
+        <v>277</v>
+      </c>
+      <c r="G89" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>301</v>
+      </c>
+      <c r="B90" t="s">
+        <v>192</v>
+      </c>
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" t="s">
+        <v>302</v>
+      </c>
+      <c r="E90" t="s">
+        <v>16</v>
+      </c>
+      <c r="F90" t="s">
+        <v>277</v>
+      </c>
+      <c r="G90" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>303</v>
+      </c>
+      <c r="B91" t="s">
+        <v>304</v>
+      </c>
+      <c r="C91" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" t="s">
+        <v>305</v>
+      </c>
+      <c r="E91" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91" t="s">
+        <v>277</v>
+      </c>
+      <c r="G91" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>308</v>
+      </c>
+      <c r="B92" t="s">
+        <v>309</v>
+      </c>
+      <c r="C92" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" t="s">
+        <v>310</v>
+      </c>
+      <c r="E92" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92" t="s">
+        <v>277</v>
+      </c>
+      <c r="G92" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>311</v>
+      </c>
+      <c r="B93" t="s">
+        <v>46</v>
+      </c>
+      <c r="C93" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" t="s">
+        <v>312</v>
+      </c>
+      <c r="E93" t="s">
+        <v>16</v>
+      </c>
+      <c r="F93" t="s">
+        <v>277</v>
+      </c>
+      <c r="G93" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>313</v>
+      </c>
+      <c r="B94" t="s">
+        <v>314</v>
+      </c>
+      <c r="C94" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" t="s">
+        <v>315</v>
+      </c>
+      <c r="E94" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94" t="s">
+        <v>277</v>
+      </c>
+      <c r="G94" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>316</v>
+      </c>
+      <c r="B95" t="s">
+        <v>317</v>
+      </c>
+      <c r="C95" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" t="s">
+        <v>318</v>
+      </c>
+      <c r="E95" t="s">
+        <v>16</v>
+      </c>
+      <c r="F95" t="s">
+        <v>277</v>
+      </c>
+      <c r="G95" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>319</v>
+      </c>
+      <c r="B96" t="s">
+        <v>320</v>
+      </c>
+      <c r="C96" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" t="s">
+        <v>321</v>
+      </c>
+      <c r="E96" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" t="s">
+        <v>277</v>
+      </c>
+      <c r="G96" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>322</v>
+      </c>
+      <c r="B97" t="s">
+        <v>109</v>
+      </c>
+      <c r="C97" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97" t="s">
+        <v>323</v>
+      </c>
+      <c r="E97" t="s">
+        <v>16</v>
+      </c>
+      <c r="F97" t="s">
+        <v>277</v>
+      </c>
+      <c r="G97" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>324</v>
+      </c>
+      <c r="B98" t="s">
+        <v>287</v>
+      </c>
+      <c r="C98" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" t="s">
+        <v>325</v>
+      </c>
+      <c r="E98" t="s">
+        <v>16</v>
+      </c>
+      <c r="F98" t="s">
+        <v>277</v>
+      </c>
+      <c r="G98" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>326</v>
+      </c>
+      <c r="B99" t="s">
+        <v>327</v>
+      </c>
+      <c r="C99" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" t="s">
+        <v>328</v>
+      </c>
+      <c r="E99" t="s">
+        <v>16</v>
+      </c>
+      <c r="F99" t="s">
+        <v>277</v>
+      </c>
+      <c r="G99" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>329</v>
+      </c>
+      <c r="B100" t="s">
+        <v>330</v>
+      </c>
+      <c r="C100" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" t="s">
+        <v>331</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="F100" t="s">
+        <v>277</v>
+      </c>
+      <c r="G100" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>332</v>
+      </c>
+      <c r="B101" t="s">
+        <v>333</v>
+      </c>
+      <c r="C101" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" t="s">
+        <v>334</v>
+      </c>
+      <c r="E101" s="6" t="s">
         <v>870</v>
       </c>
-      <c r="F77" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G77" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="C78" s="6" t="s">
+      <c r="F101" t="s">
+        <v>277</v>
+      </c>
+      <c r="G101" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>335</v>
+      </c>
+      <c r="B102" t="s">
+        <v>336</v>
+      </c>
+      <c r="C102" t="s">
         <v>9</v>
       </c>
-      <c r="D78" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="C79" s="6" t="s">
+      <c r="D102" t="s">
+        <v>337</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F102" t="s">
+        <v>277</v>
+      </c>
+      <c r="G102" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>338</v>
+      </c>
+      <c r="B103" t="s">
+        <v>339</v>
+      </c>
+      <c r="C103" t="s">
         <v>9</v>
       </c>
-      <c r="D79" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G81" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F84" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="F88" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G89" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G95" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>873</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G102" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>874</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="6" t="s">
+      <c r="D103" t="s">
         <v>340</v>
       </c>
-      <c r="B104" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="E104" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G104" s="6" t="s">
-        <v>232</v>
+      <c r="E103" t="s">
+        <v>16</v>
+      </c>
+      <c r="F103" t="s">
+        <v>277</v>
+      </c>
+      <c r="G103" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -5483,16 +5450,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -5503,22 +5470,22 @@
     </row>
     <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>346</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>348</v>
       </c>
       <c r="D2" s="4">
         <v>120000000</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>12</v>
@@ -5526,13 +5493,13 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D3" s="4">
         <v>120000000</v>
@@ -5541,7 +5508,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>12</v>
@@ -5549,22 +5516,22 @@
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>354</v>
       </c>
       <c r="D4" s="4">
         <v>100000000</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>12</v>
@@ -5572,22 +5539,22 @@
     </row>
     <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D5" s="4">
         <v>90000000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>12</v>
@@ -5595,22 +5562,22 @@
     </row>
     <row r="6" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>359</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>361</v>
       </c>
       <c r="D6" s="4">
         <v>14000000</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>12</v>
@@ -5618,22 +5585,22 @@
     </row>
     <row r="7" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D7" s="4">
         <v>260000000</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>12</v>
@@ -5641,22 +5608,22 @@
     </row>
     <row r="8" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D8" s="4">
         <v>45000000</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>12</v>
@@ -5664,22 +5631,22 @@
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D9" s="4">
         <v>5000000</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>12</v>
@@ -5687,22 +5654,22 @@
     </row>
     <row r="10" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>374</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>12</v>
@@ -5710,22 +5677,22 @@
     </row>
     <row r="11" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D11" s="4">
         <v>50000000</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>12</v>
@@ -5733,22 +5700,22 @@
     </row>
     <row r="12" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D12" s="4">
         <v>1600000</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>12</v>
@@ -5756,22 +5723,22 @@
     </row>
     <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D13" s="4">
         <v>28000000</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>12</v>
@@ -5779,22 +5746,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D14" s="4">
         <v>31000000</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>12</v>
@@ -5802,22 +5769,22 @@
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D15" s="4">
         <v>35000000</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>12</v>
@@ -5825,22 +5792,22 @@
     </row>
     <row r="16" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D16" s="4">
         <v>115000000</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>12</v>
@@ -5848,22 +5815,22 @@
     </row>
     <row r="17" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D17" s="4">
         <v>80000000</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>12</v>
@@ -5871,22 +5838,22 @@
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>398</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>12</v>
@@ -5894,22 +5861,22 @@
     </row>
     <row r="19" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D19" s="4">
         <v>57700000</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>59</v>
@@ -5917,22 +5884,22 @@
     </row>
     <row r="20" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D20" s="4">
         <v>31000000</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>59</v>
@@ -5940,13 +5907,13 @@
     </row>
     <row r="21" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D21" s="4">
         <v>14000000</v>
@@ -5955,7 +5922,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>59</v>
@@ -5963,22 +5930,22 @@
     </row>
     <row r="22" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D22" s="4">
         <v>9300000</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>59</v>
@@ -5986,13 +5953,13 @@
     </row>
     <row r="23" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D23" s="4">
         <v>1200000</v>
@@ -6001,7 +5968,7 @@
         <v>16</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>59</v>
@@ -6009,22 +5976,22 @@
     </row>
     <row r="24" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D24" s="4">
         <v>100000000</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>59</v>
@@ -6032,22 +5999,22 @@
     </row>
     <row r="25" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D25" s="4">
         <v>7700000</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>59</v>
@@ -6055,13 +6022,13 @@
     </row>
     <row r="26" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D26" s="4">
         <v>20000000</v>
@@ -6070,7 +6037,7 @@
         <v>16</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>59</v>
@@ -6078,22 +6045,22 @@
     </row>
     <row r="27" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D27" s="4">
         <v>15000000</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>59</v>
@@ -6101,22 +6068,22 @@
     </row>
     <row r="28" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D28" s="4">
         <v>142000000</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>59</v>
@@ -6124,22 +6091,22 @@
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D29" s="4">
         <v>17500000</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>59</v>
@@ -6147,22 +6114,22 @@
     </row>
     <row r="30" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D30" s="4">
         <v>7300000</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>59</v>
@@ -6170,22 +6137,22 @@
     </row>
     <row r="31" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D31" s="4">
         <v>11000000</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>59</v>
@@ -6193,22 +6160,22 @@
     </row>
     <row r="32" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D32" s="4">
         <v>42000000</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>59</v>
@@ -6216,22 +6183,22 @@
     </row>
     <row r="33" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D33" s="4">
         <v>13600000</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>59</v>
@@ -6239,22 +6206,22 @@
     </row>
     <row r="34" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D34" s="4">
         <v>12700000</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>59</v>
@@ -6262,22 +6229,22 @@
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D35" s="4">
         <v>2000000</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>59</v>
@@ -6285,22 +6252,22 @@
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>448</v>
-      </c>
       <c r="F36" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>59</v>
@@ -6308,22 +6275,22 @@
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D37" s="4">
         <v>2300000</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>59</v>
@@ -6331,22 +6298,22 @@
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D38" s="4">
         <v>15000000</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>59</v>
@@ -6354,22 +6321,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>457</v>
-      </c>
       <c r="F39" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>59</v>
@@ -6377,22 +6344,22 @@
     </row>
     <row r="40" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D40" s="4">
         <v>100000000</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>91</v>
@@ -6400,22 +6367,22 @@
     </row>
     <row r="41" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>463</v>
-      </c>
       <c r="F41" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>91</v>
@@ -6423,13 +6390,13 @@
     </row>
     <row r="42" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D42" s="4">
         <v>175000000</v>
@@ -6438,7 +6405,7 @@
         <v>88</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>91</v>
@@ -6446,22 +6413,22 @@
     </row>
     <row r="43" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D43" s="4">
         <v>200000000</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>91</v>
@@ -6469,22 +6436,22 @@
     </row>
     <row r="44" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D44" s="4">
         <v>40000000</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>91</v>
@@ -6492,22 +6459,22 @@
     </row>
     <row r="45" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D45" s="4">
         <v>11700000</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>91</v>
@@ -6515,22 +6482,22 @@
     </row>
     <row r="46" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D46" s="4">
         <v>65000000</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>91</v>
@@ -6538,22 +6505,22 @@
     </row>
     <row r="47" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D47" s="4">
         <v>53000000</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>91</v>
@@ -6561,22 +6528,22 @@
     </row>
     <row r="48" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D48" s="4">
         <v>120000000</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>91</v>
@@ -6584,22 +6551,22 @@
     </row>
     <row r="49" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D49" s="4">
         <v>5000000</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>91</v>
@@ -6607,22 +6574,22 @@
     </row>
     <row r="50" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D50" s="4">
         <v>7000000</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>91</v>
@@ -6630,22 +6597,22 @@
     </row>
     <row r="51" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D51" s="4">
         <v>17780000</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>91</v>
@@ -6653,22 +6620,22 @@
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D52" s="4">
         <v>24000000</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>91</v>
@@ -6676,22 +6643,22 @@
     </row>
     <row r="53" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D53" s="4">
         <v>65000000</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>91</v>
@@ -6699,22 +6666,22 @@
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D54" s="4">
         <v>175000000</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>91</v>
@@ -6722,22 +6689,22 @@
     </row>
     <row r="55" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D55" s="4">
         <v>13000000</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>91</v>
@@ -6745,22 +6712,22 @@
     </row>
     <row r="56" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D56" s="4">
         <v>10900000</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>91</v>
@@ -6768,22 +6735,22 @@
     </row>
     <row r="57" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D57" s="4">
         <v>25000000</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>91</v>
@@ -6791,22 +6758,22 @@
     </row>
     <row r="58" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D58" s="4">
         <v>83000000</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>91</v>
@@ -6814,13 +6781,13 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D59" s="4">
         <v>30000000</v>
@@ -6829,7 +6796,7 @@
         <v>16</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>91</v>
@@ -6837,22 +6804,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D60" s="4">
         <v>5200000</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>91</v>
@@ -6860,22 +6827,22 @@
     </row>
     <row r="61" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D61" s="4">
         <v>100000000</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>123</v>
@@ -6883,22 +6850,22 @@
     </row>
     <row r="62" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D62" s="4">
         <v>1700000</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>123</v>
@@ -6906,22 +6873,22 @@
     </row>
     <row r="63" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D63" s="4">
         <v>200000000</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>123</v>
@@ -6929,22 +6896,22 @@
     </row>
     <row r="64" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D64" s="4">
         <v>38000000</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>123</v>
@@ -6952,22 +6919,22 @@
     </row>
     <row r="65" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D65" s="4">
         <v>31000000</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>123</v>
@@ -6975,22 +6942,22 @@
     </row>
     <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D66" s="4">
         <v>2000000</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>123</v>
@@ -6998,22 +6965,22 @@
     </row>
     <row r="67" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D67" s="4">
         <v>3000000</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>123</v>
@@ -7021,22 +6988,22 @@
     </row>
     <row r="68" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D68" s="4">
         <v>7500000</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>123</v>
@@ -7044,22 +7011,22 @@
     </row>
     <row r="69" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D69" s="4">
         <v>30000000</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>123</v>
@@ -7067,22 +7034,22 @@
     </row>
     <row r="70" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D70" s="4">
         <v>11500000</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>123</v>
@@ -7090,22 +7057,22 @@
     </row>
     <row r="71" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D71" s="4">
         <v>15000000</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>123</v>
@@ -7113,22 +7080,22 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D72" s="4">
         <v>35000000</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>123</v>
@@ -7136,22 +7103,22 @@
     </row>
     <row r="73" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D73" s="4">
         <v>9000000</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>123</v>
@@ -7159,22 +7126,22 @@
     </row>
     <row r="74" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>560</v>
-      </c>
       <c r="F74" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>123</v>
@@ -7182,22 +7149,22 @@
     </row>
     <row r="75" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D75" s="4">
         <v>35000000</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>123</v>
@@ -7205,22 +7172,22 @@
     </row>
     <row r="76" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D76" s="4">
         <v>10000000</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>123</v>
@@ -7228,22 +7195,22 @@
     </row>
     <row r="77" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>569</v>
-      </c>
       <c r="F77" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>123</v>
@@ -7251,22 +7218,22 @@
     </row>
     <row r="78" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D78" s="4">
         <v>14400000</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>123</v>
@@ -7274,22 +7241,22 @@
     </row>
     <row r="79" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D79" s="4">
         <v>6000000</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>123</v>
@@ -7297,22 +7264,22 @@
     </row>
     <row r="80" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D80" s="4">
         <v>25000000</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>123</v>
@@ -7320,22 +7287,22 @@
     </row>
     <row r="81" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D81" s="4">
         <v>2000000</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>123</v>
@@ -7343,22 +7310,22 @@
     </row>
     <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D82" s="4">
         <v>14300000</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>123</v>
@@ -7366,22 +7333,22 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D83" s="4">
         <v>3175000</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>123</v>
@@ -7389,22 +7356,22 @@
     </row>
     <row r="84" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D84" s="4">
         <v>1200000</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>123</v>
@@ -7412,22 +7379,22 @@
     </row>
     <row r="85" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D85" s="4">
         <v>1270000</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>123</v>
@@ -7435,22 +7402,22 @@
     </row>
     <row r="86" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D86" s="4">
         <v>20000000</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>123</v>
@@ -7458,22 +7425,22 @@
     </row>
     <row r="87" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D87" s="4">
         <v>200000</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>123</v>
@@ -7481,13 +7448,13 @@
     </row>
     <row r="88" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D88" s="4">
         <v>13500000</v>
@@ -7496,7 +7463,7 @@
         <v>16</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>163</v>
@@ -7504,22 +7471,22 @@
     </row>
     <row r="89" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D89" s="4">
         <v>10000000</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>163</v>
@@ -7527,22 +7494,22 @@
     </row>
     <row r="90" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D90" s="4">
         <v>42000000</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>163</v>
@@ -7550,22 +7517,22 @@
     </row>
     <row r="91" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D91" s="4">
         <v>45000000</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>163</v>
@@ -7573,22 +7540,22 @@
     </row>
     <row r="92" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D92" s="4">
         <v>4500000</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>163</v>
@@ -7596,22 +7563,22 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>163</v>
@@ -7619,22 +7586,22 @@
     </row>
     <row r="94" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D94" s="4">
         <v>900000</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>163</v>
@@ -7642,22 +7609,22 @@
     </row>
     <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>621</v>
-      </c>
       <c r="F95" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>163</v>
@@ -7665,22 +7632,22 @@
     </row>
     <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D96" s="4">
         <v>36100000</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>163</v>
@@ -7688,22 +7655,22 @@
     </row>
     <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D97" s="4">
         <v>4000000</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>163</v>
@@ -7711,22 +7678,22 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D98" s="4">
         <v>2500000</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>163</v>
@@ -7734,22 +7701,22 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D99" s="4">
         <v>2500000</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>163</v>
@@ -7757,22 +7724,22 @@
     </row>
     <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D100" s="4">
         <v>4500000</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>163</v>
@@ -7780,13 +7747,13 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>16</v>
@@ -7795,7 +7762,7 @@
         <v>16</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>163</v>
@@ -7803,22 +7770,22 @@
     </row>
     <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>641</v>
-      </c>
       <c r="F102" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>163</v>
@@ -7826,22 +7793,22 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D103" s="4">
         <v>1524000</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>163</v>
@@ -7849,22 +7816,22 @@
     </row>
     <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D104" s="4">
         <v>17900000</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>200</v>
@@ -7872,22 +7839,22 @@
     </row>
     <row r="105" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>650</v>
-      </c>
       <c r="F105" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>200</v>
@@ -7895,22 +7862,22 @@
     </row>
     <row r="106" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>653</v>
-      </c>
       <c r="F106" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>200</v>
@@ -7918,22 +7885,22 @@
     </row>
     <row r="107" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D107" s="4">
         <v>6000000</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>200</v>
@@ -7941,22 +7908,22 @@
     </row>
     <row r="108" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D108" s="4">
         <v>20000000</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>200</v>
@@ -7964,22 +7931,22 @@
     </row>
     <row r="109" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D109" s="4">
         <v>16000000</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>200</v>
@@ -7987,22 +7954,22 @@
     </row>
     <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D110" s="4">
         <v>1180000</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>200</v>
@@ -8010,22 +7977,22 @@
     </row>
     <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D111" s="4">
         <v>6000000</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>200</v>
@@ -8033,22 +8000,22 @@
     </row>
     <row r="112" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D112" s="4">
         <v>7909999</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>200</v>
@@ -8056,13 +8023,13 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D113" s="4">
         <v>29400000</v>
@@ -8071,7 +8038,7 @@
         <v>16</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>200</v>
@@ -8079,22 +8046,22 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D114" s="4">
         <v>370000</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>200</v>
@@ -8102,22 +8069,22 @@
     </row>
     <row r="115" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="B115" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>679</v>
-      </c>
       <c r="F115" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>200</v>
@@ -8125,13 +8092,13 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D116" s="4">
         <v>7500000</v>
@@ -8140,7 +8107,7 @@
         <v>16</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>200</v>
@@ -8148,22 +8115,22 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D117" s="4">
         <v>1800000</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>200</v>
@@ -8171,22 +8138,22 @@
     </row>
     <row r="118" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D118" s="4">
         <v>2300000</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>200</v>
@@ -8194,10 +8161,10 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>209</v>
@@ -8206,323 +8173,323 @@
         <v>50000000</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D120" s="4">
         <v>2000000</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="B121" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>694</v>
-      </c>
       <c r="F121" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D122" s="4">
         <v>450000000</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D123" s="4">
         <v>27300000</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D124" s="4">
         <v>11500000</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D125" s="4">
         <v>30000000</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D126" s="4">
         <v>20000000</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D127" s="4">
         <v>10000000</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D128" s="4">
         <v>56000000</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D129" s="4">
         <v>12000000</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D130" s="4">
         <v>20000000</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D131" s="4">
         <v>27500000</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D132" s="4">
         <v>4700000</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D133" s="4">
         <v>14000000</v>
@@ -8531,527 +8498,527 @@
         <v>16</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D134" s="4">
         <v>250000</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D135" s="4">
         <v>1200000</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D136" s="4">
         <v>11000000</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D137" s="4">
         <v>40000000</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E138" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>742</v>
-      </c>
       <c r="F138" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D139" s="4">
         <v>16000000</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E140" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="B140" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>748</v>
-      </c>
       <c r="F140" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D141" s="4">
         <v>2500000</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D142" s="4">
         <v>12000000</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D143" s="4">
         <v>1440000</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D144" s="4">
         <v>2857500</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D145" s="4">
         <v>2300000</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D146" s="4">
         <v>35000000</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D147" s="4">
         <v>50000000</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D148" s="4">
         <v>8200000</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D149" s="4">
         <v>4500000</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D150" s="4">
         <v>75000000</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D151" s="4">
         <v>24000000</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D152" s="4">
         <v>16000000</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D153" s="4">
         <v>8000000</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D154" s="4">
         <v>1304000</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D155" s="4">
         <v>400000</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="D156" s="4">
         <v>7000000</v>
@@ -9060,7 +9027,7 @@
         <v>16</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>215</v>
@@ -9068,22 +9035,22 @@
     </row>
     <row r="157" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D157" s="4">
         <v>67000000</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>215</v>
@@ -9091,22 +9058,22 @@
     </row>
     <row r="158" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D158" s="4">
         <v>10000000</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>215</v>
@@ -9114,22 +9081,22 @@
     </row>
     <row r="159" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D159" s="4">
         <v>120000000</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>215</v>
@@ -9137,22 +9104,22 @@
     </row>
     <row r="160" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D160" s="4">
         <v>85000000</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G160" s="3" t="s">
         <v>215</v>
@@ -9160,22 +9127,22 @@
     </row>
     <row r="161" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D161" s="4">
         <v>162500000</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>215</v>
@@ -9183,22 +9150,22 @@
     </row>
     <row r="162" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D162" s="4">
         <v>60000000</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>215</v>
@@ -9206,22 +9173,22 @@
     </row>
     <row r="163" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D163" s="4">
         <v>238000000</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>215</v>
@@ -9229,22 +9196,22 @@
     </row>
     <row r="164" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="D164" s="4">
         <v>8000000</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>215</v>
@@ -9252,22 +9219,22 @@
     </row>
     <row r="165" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D165" s="4">
         <v>316700000</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>215</v>
@@ -9275,22 +9242,22 @@
     </row>
     <row r="166" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="D166" s="4">
         <v>170000000</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G166" s="3" t="s">
         <v>215</v>
@@ -9298,22 +9265,22 @@
     </row>
     <row r="167" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D167" s="4">
         <v>130000000</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>215</v>
@@ -9321,22 +9288,22 @@
     </row>
     <row r="168" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D168" s="4">
         <v>110000000</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>215</v>
@@ -9344,22 +9311,22 @@
     </row>
     <row r="169" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D169" s="4">
         <v>65000000</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>215</v>
@@ -9367,22 +9334,22 @@
     </row>
     <row r="170" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D170" s="4">
         <v>104000000</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G170" s="3" t="s">
         <v>215</v>
@@ -9390,22 +9357,22 @@
     </row>
     <row r="171" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D171" s="4">
         <v>16000000</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>215</v>
@@ -9413,22 +9380,22 @@
     </row>
     <row r="172" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="D172" s="4">
         <v>1270000</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>215</v>
@@ -9439,7 +9406,7 @@
         <v>208</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>209</v>
@@ -9448,10 +9415,10 @@
         <v>50000000</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>215</v>
@@ -9459,22 +9426,22 @@
     </row>
     <row r="174" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D174" s="4">
         <v>323850</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>215</v>
@@ -9482,22 +9449,22 @@
     </row>
     <row r="175" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E175" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="B175" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>847</v>
-      </c>
-      <c r="D175" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E175" s="3" t="s">
-        <v>848</v>
-      </c>
       <c r="F175" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G175" s="3" t="s">
         <v>215</v>
@@ -9505,22 +9472,22 @@
     </row>
     <row r="176" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E176" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="B176" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>850</v>
-      </c>
-      <c r="D176" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E176" s="3" t="s">
-        <v>851</v>
-      </c>
       <c r="F176" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G176" s="3" t="s">
         <v>215</v>
@@ -9528,22 +9495,22 @@
     </row>
     <row r="177" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D177" s="4">
         <v>2800000</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>215</v>
@@ -9551,22 +9518,22 @@
     </row>
     <row r="178" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D178" s="4">
         <v>85000000</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>215</v>
@@ -9574,22 +9541,22 @@
     </row>
     <row r="179" spans="1:7" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D179" s="4">
         <v>100000000</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>215</v>
@@ -9597,13 +9564,13 @@
     </row>
     <row r="180" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D180" s="4">
         <v>4875000</v>
@@ -9612,7 +9579,7 @@
         <v>16</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>215</v>
@@ -9620,13 +9587,13 @@
     </row>
     <row r="181" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D181" s="4">
         <v>5000000</v>
@@ -9635,7 +9602,7 @@
         <v>16</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>215</v>
@@ -9643,22 +9610,22 @@
     </row>
     <row r="182" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D182" s="4">
         <v>90000000</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>211</v>
@@ -9666,22 +9633,22 @@
     </row>
     <row r="183" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="D183" s="4">
         <v>10000000</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>211</v>

--- a/data/MedTech_YTD_Standardized.xlsx
+++ b/data/MedTech_YTD_Standardized.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beacononehcp-my.sharepoint.com/personal/hannah_peric_beacononehcp_com/Documents/Documents/medtech-dashboard/Medtech-Dashboard-M-A/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F96785DA-9CED-407A-8B28-F40B00A2853E}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18195456-0793-405C-9907-0F325E985402}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD M&amp;A Activity" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1959" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="924">
   <si>
     <t>Company</t>
   </si>
@@ -2691,9 +2691,6 @@
     <t>Edison histotripsy system; focused ultrasound tissue destruction.</t>
   </si>
   <si>
-    <t>$2.25 billion</t>
-  </si>
-  <si>
     <t>SiVantage</t>
   </si>
   <si>
@@ -2703,9 +2700,6 @@
     <t>SImmetry and SImmetry+ sacro-pelvic fusion technologies.</t>
   </si>
   <si>
-    <t>Not disclosed</t>
-  </si>
-  <si>
     <t>Conference</t>
   </si>
   <si>
@@ -2718,51 +2712,33 @@
     <t>BLOOM⁴³ wearable prehabilitation device for breast surgery patients.</t>
   </si>
   <si>
-    <t>$4.5 million</t>
-  </si>
-  <si>
     <t>CLiKX handheld robotic device for needle-free ear tube surgery.</t>
   </si>
   <si>
-    <t>$7.5 million</t>
-  </si>
-  <si>
     <t>Wingwomen</t>
   </si>
   <si>
     <t>NINA AI-powered digital vaginal speculum and cloud bioinformatics.</t>
   </si>
   <si>
-    <t>$2 million</t>
-  </si>
-  <si>
     <t>Private investors</t>
   </si>
   <si>
     <t>AI-powered patient monitoring platform; Series A to expand U.S. ops.</t>
   </si>
   <si>
-    <t>$11.6 million</t>
-  </si>
-  <si>
     <t>We Venture Capital, ClavystBio; with Adaptive Capital Partners, Mayo Foundation, others</t>
   </si>
   <si>
     <t>HOTWIRE™ left-heart transseptal access system; follow-on financing.</t>
   </si>
   <si>
-    <t>$29.4 million</t>
-  </si>
-  <si>
     <t>Mentaily</t>
   </si>
   <si>
     <t>LIV AI platform simulating psychiatric intake for early triage.</t>
   </si>
   <si>
-    <t>$3 million</t>
-  </si>
-  <si>
     <t>Beta Bionics</t>
   </si>
   <si>
@@ -2772,49 +2748,52 @@
     <t>NASDAQ listing</t>
   </si>
   <si>
-    <t>$235 M</t>
-  </si>
-  <si>
     <t>Kestra Medical Technologies</t>
   </si>
   <si>
     <t>Wearable cardiac monitoring &amp; defibrillation</t>
   </si>
   <si>
-    <t>$232 M</t>
-  </si>
-  <si>
     <t>Caris Life Sciences</t>
   </si>
   <si>
     <t>Precision oncology &amp; molecular diagnostics</t>
   </si>
   <si>
-    <t>$494 M</t>
-  </si>
-  <si>
     <t>Capsule endoscopy imaging system</t>
   </si>
   <si>
-    <t>$28 M</t>
-  </si>
-  <si>
     <t>Carlsmed</t>
   </si>
   <si>
     <t>AI-driven spine surgery planning</t>
   </si>
   <si>
-    <t>$101 M</t>
-  </si>
-  <si>
     <t>AI-based cardiac imaging FFR-CT</t>
   </si>
   <si>
     <t>NYSE listing</t>
   </si>
   <si>
-    <t>$364 M</t>
+    <t>$2250000000</t>
+  </si>
+  <si>
+    <t>$235000000</t>
+  </si>
+  <si>
+    <t>$232000000</t>
+  </si>
+  <si>
+    <t>$494000000</t>
+  </si>
+  <si>
+    <t>$28000000</t>
+  </si>
+  <si>
+    <t>$101000000</t>
+  </si>
+  <si>
+    <t>$364000000</t>
   </si>
 </sst>
 </file>
@@ -2840,7 +2819,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2851,12 +2830,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
         <bgColor rgb="FF4472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF59D"/>
-        <bgColor rgb="FFFFF59D"/>
       </patternFill>
     </fill>
   </fills>
@@ -2887,7 +2860,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2904,12 +2877,22 @@
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3258,7 +3241,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4772,7 +4755,7 @@
         <v>215</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -5712,55 +5695,55 @@
       <c r="H103" s="6"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="8" t="s">
+      <c r="A104" s="11" t="s">
         <v>886</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="B104" s="11" t="s">
         <v>887</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="C104" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D104" s="8" t="s">
+      <c r="D104" s="11" t="s">
         <v>888</v>
       </c>
-      <c r="E104" s="8" t="s">
+      <c r="E104" s="12" t="s">
+        <v>917</v>
+      </c>
+      <c r="F104" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="G104" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="H104" s="11" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="11" t="s">
         <v>889</v>
       </c>
-      <c r="F104" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="G104" s="8" t="s">
+      <c r="B105" s="11" t="s">
+        <v>890</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>891</v>
+      </c>
+      <c r="E105" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F105" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="G105" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="H104" s="8" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="8" t="s">
-        <v>890</v>
-      </c>
-      <c r="B105" s="8" t="s">
-        <v>891</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D105" s="8" t="s">
-        <v>892</v>
-      </c>
-      <c r="E105" s="8" t="s">
+      <c r="H105" s="11" t="s">
         <v>893</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="G105" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="H105" s="8" t="s">
-        <v>895</v>
       </c>
     </row>
   </sheetData>
@@ -5807,7 +5790,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -10020,7 +10003,7 @@
       <c r="C177" s="2" t="s">
         <v>851</v>
       </c>
-      <c r="D177" s="3">
+      <c r="D177" s="14">
         <v>2800000</v>
       </c>
       <c r="E177" s="2" t="s">
@@ -10044,7 +10027,7 @@
       <c r="C178" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="D178" s="3">
+      <c r="D178" s="14">
         <v>85000000</v>
       </c>
       <c r="E178" s="2" t="s">
@@ -10068,7 +10051,7 @@
       <c r="C179" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="D179" s="3">
+      <c r="D179" s="14">
         <v>100000000</v>
       </c>
       <c r="E179" s="2" t="s">
@@ -10092,7 +10075,7 @@
       <c r="C180" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="D180" s="3">
+      <c r="D180" s="14">
         <v>4875000</v>
       </c>
       <c r="E180" s="2" t="s">
@@ -10116,7 +10099,7 @@
       <c r="C181" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="D181" s="3">
+      <c r="D181" s="14">
         <v>5000000</v>
       </c>
       <c r="E181" s="2" t="s">
@@ -10140,7 +10123,7 @@
       <c r="C182" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="D182" s="3">
+      <c r="D182" s="14">
         <v>90000000</v>
       </c>
       <c r="E182" s="2" t="s">
@@ -10164,7 +10147,7 @@
       <c r="C183" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="D183" s="3">
+      <c r="D183" s="14">
         <v>10000000</v>
       </c>
       <c r="E183" s="2" t="s">
@@ -10180,16 +10163,16 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>345</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>897</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
+      </c>
+      <c r="D184" s="10">
+        <v>4500000</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>16</v>
@@ -10201,7 +10184,7 @@
         <v>231</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -10212,10 +10195,10 @@
         <v>345</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>900</v>
+        <v>896</v>
+      </c>
+      <c r="D185" s="10">
+        <v>7500000</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>16</v>
@@ -10227,24 +10210,24 @@
         <v>200</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>345</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="D186" s="2" t="s">
-        <v>903</v>
+        <v>898</v>
+      </c>
+      <c r="D186" s="10">
+        <v>2000000</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>872</v>
@@ -10253,7 +10236,7 @@
         <v>91</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -10264,13 +10247,13 @@
         <v>345</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>905</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>906</v>
+        <v>900</v>
+      </c>
+      <c r="D187" s="10">
+        <v>11600000</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>277</v>
@@ -10279,7 +10262,7 @@
         <v>231</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -10290,10 +10273,10 @@
         <v>345</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>909</v>
+        <v>902</v>
+      </c>
+      <c r="D188" s="10">
+        <v>29400000</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>16</v>
@@ -10305,21 +10288,21 @@
         <v>200</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>345</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>912</v>
+        <v>904</v>
+      </c>
+      <c r="D189" s="10">
+        <v>3000000</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>16</v>
@@ -10331,7 +10314,7 @@
         <v>163</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
   </sheetData>
@@ -10394,7 +10377,7 @@
       <c r="F2" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="9">
         <v>45898</v>
       </c>
     </row>
@@ -10417,145 +10400,145 @@
       <c r="F3" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>45868</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>918</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="G4" s="9">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>919</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="G5" s="9">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>911</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>920</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="G6" s="9">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>912</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>921</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="G7" s="9">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>913</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>914</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D8" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>922</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="G8" s="9">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>915</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>916</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>872</v>
-      </c>
-      <c r="G4" s="10">
-        <v>45658</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>917</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>918</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>915</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>919</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>872</v>
-      </c>
-      <c r="G5" s="10">
-        <v>45717</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>920</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>921</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>915</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>922</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>873</v>
-      </c>
-      <c r="G6" s="10">
-        <v>45809</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="E9" s="13" t="s">
         <v>923</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>915</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>924</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="G7" s="10">
-        <v>45839</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>925</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>926</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>915</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>927</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="G8" s="10">
-        <v>45870</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>817</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>928</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>929</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>930</v>
-      </c>
       <c r="F9" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>45901</v>
       </c>
     </row>

--- a/data/MedTech_YTD_Standardized.xlsx
+++ b/data/MedTech_YTD_Standardized.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beacononehcp-my.sharepoint.com/personal/hannah_peric_beacononehcp_com/Documents/Documents/medtech-dashboard/Medtech-Dashboard-M-A/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18195456-0793-405C-9907-0F325E985402}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{333F7B8D-B0BB-4698-A44B-B355772C16C5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD M&amp;A Activity" sheetId="1" r:id="rId1"/>
@@ -2860,19 +2860,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2883,17 +2877,19 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3245,2504 +3241,2504 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="6"/>
+      <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="6"/>
+      <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="6"/>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="6"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="6"/>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="6"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="6"/>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="6"/>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="6"/>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="6"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="6"/>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="6"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H14" s="6"/>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="6"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="6"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="6"/>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H18" s="6"/>
+      <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H19" s="6"/>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H20" s="6"/>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H21" s="6"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H22" s="6"/>
+      <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H23" s="6"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H24" s="6"/>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H25" s="6"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H26" s="6"/>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H27" s="6"/>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="6"/>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H29" s="6"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H30" s="6"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H31" s="6"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H32" s="6"/>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H33" s="6"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H34" s="6"/>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H35" s="6"/>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H36" s="6"/>
+      <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="G37" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H37" s="6"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H38" s="6"/>
+      <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H39" s="6"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H40" s="6"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H41" s="6"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H42" s="6"/>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G43" s="6" t="s">
+      <c r="G43" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H43" s="6"/>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H44" s="6"/>
+      <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G45" s="6" t="s">
+      <c r="G45" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H45" s="6"/>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H46" s="6"/>
+      <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="G47" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H47" s="6"/>
+      <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F48" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="G48" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H48" s="6"/>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G49" s="6" t="s">
+      <c r="G49" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H49" s="6"/>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H50" s="6"/>
+      <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G51" s="6" t="s">
+      <c r="G51" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H51" s="6"/>
+      <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H52" s="6"/>
+      <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F53" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="G53" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H53" s="6"/>
+      <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="G54" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H54" s="6"/>
+      <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G55" s="6" t="s">
+      <c r="G55" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H55" s="6"/>
+      <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E56" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="G56" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H56" s="6"/>
+      <c r="H56" s="4"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E57" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G57" s="6" t="s">
+      <c r="G57" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="H57" s="6"/>
+      <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E58" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G58" s="6" t="s">
+      <c r="G58" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="H58" s="6"/>
+      <c r="H58" s="4"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F59" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G59" s="6" t="s">
+      <c r="G59" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="H59" s="6"/>
+      <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D60" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E60" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="F60" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G60" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="H60" s="6"/>
+      <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D61" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E61" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F61" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G61" s="6" t="s">
+      <c r="F61" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G61" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H61" s="6"/>
+      <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="D62" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="E62" s="6" t="s">
+      <c r="E62" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="F62" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G62" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H62" s="6"/>
+      <c r="H62" s="4"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D63" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="F63" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G63" s="6" t="s">
+      <c r="F63" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G63" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H63" s="6"/>
+      <c r="H63" s="4"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D64" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E64" s="6" t="s">
+      <c r="E64" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="F64" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G64" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H64" s="6" t="s">
+      <c r="H64" s="4" t="s">
         <v>893</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="F65" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G65" s="6" t="s">
+      <c r="F65" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G65" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H65" s="6"/>
+      <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D66" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="E66" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="F66" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H66" s="6"/>
+      <c r="H66" s="4"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="E67" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="F67" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G67" s="6" t="s">
+      <c r="F67" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G67" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H67" s="6"/>
+      <c r="H67" s="4"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E68" s="6" t="s">
+      <c r="E68" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="F68" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G68" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H68" s="6"/>
+      <c r="H68" s="4"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E69" s="6" t="s">
+      <c r="E69" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F69" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G69" s="6" t="s">
+      <c r="F69" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G69" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H69" s="6"/>
+      <c r="H69" s="4"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E70" s="6" t="s">
+      <c r="E70" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F70" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G70" s="6" t="s">
+      <c r="F70" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H70" s="6"/>
+      <c r="H70" s="4"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D71" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E71" s="6" t="s">
+      <c r="E71" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F71" s="6" t="s">
+      <c r="F71" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G71" s="6" t="s">
+      <c r="G71" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="H71" s="6"/>
+      <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E72" s="6" t="s">
+      <c r="E72" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F72" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G72" s="6" t="s">
+      <c r="G72" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="H72" s="6"/>
+      <c r="H72" s="4"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D73" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="E73" s="6" t="s">
+      <c r="E73" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="F73" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G73" s="6" t="s">
+      <c r="G73" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="H73" s="6"/>
+      <c r="H73" s="4"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E74" s="6" t="s">
+      <c r="E74" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F74" s="6" t="s">
+      <c r="F74" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G74" s="6" t="s">
+      <c r="G74" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H74" s="6"/>
+      <c r="H74" s="4"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D75" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="E75" s="6" t="s">
+      <c r="E75" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F75" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G75" s="6" t="s">
+      <c r="G75" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H75" s="6"/>
+      <c r="H75" s="4"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="4" t="s">
         <v>874</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="E76" s="6" t="s">
+      <c r="E76" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="G76" s="6" t="s">
+      <c r="G76" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H76" s="6"/>
+      <c r="H76" s="4"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D77" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E77" s="5" t="s">
         <v>868</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="F77" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="G77" s="6" t="s">
+      <c r="G77" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="H77" s="6"/>
+      <c r="H77" s="4"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E78" s="6" t="s">
+      <c r="E78" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F78" s="6" t="s">
+      <c r="F78" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="G78" s="6" t="s">
+      <c r="G78" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="H78" s="6"/>
+      <c r="H78" s="4"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="D79" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="E79" s="6" t="s">
+      <c r="E79" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F79" s="6" t="s">
+      <c r="F79" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="G79" s="6" t="s">
+      <c r="G79" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="H79" s="6"/>
+      <c r="H79" s="4"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="D80" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="E80" s="6" t="s">
+      <c r="E80" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F80" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="G80" s="6" t="s">
+      <c r="G80" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="H80" s="6"/>
+      <c r="H80" s="4"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="D81" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E81" s="6" t="s">
+      <c r="E81" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F81" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G81" s="6" t="s">
+      <c r="F81" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H81" s="6"/>
+      <c r="H81" s="4"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="D82" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E82" s="6" t="s">
+      <c r="E82" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F82" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G82" s="6" t="s">
+      <c r="F82" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G82" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H82" s="6"/>
+      <c r="H82" s="4"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D83" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E83" s="6" t="s">
+      <c r="E83" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F83" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G83" s="6" t="s">
+      <c r="F83" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H83" s="6"/>
+      <c r="H83" s="4"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="D84" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="E84" s="6" t="s">
+      <c r="E84" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F84" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G84" s="6" t="s">
+      <c r="F84" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G84" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H84" s="6"/>
+      <c r="H84" s="4"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C85" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="D85" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="E85" s="6" t="s">
+      <c r="E85" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F85" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G85" s="6" t="s">
+      <c r="F85" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H85" s="6"/>
+      <c r="H85" s="4"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D86" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="E86" s="6" t="s">
+      <c r="E86" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F86" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G86" s="6" t="s">
+      <c r="F86" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G86" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H86" s="6"/>
+      <c r="H86" s="4"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="B87" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C87" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D87" s="6" t="s">
+      <c r="D87" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="E87" s="6" t="s">
+      <c r="E87" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F87" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G87" s="6" t="s">
+      <c r="F87" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H87" s="6"/>
+      <c r="H87" s="4"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C88" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D88" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="E88" s="6" t="s">
+      <c r="E88" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="F88" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G88" s="6" t="s">
+      <c r="F88" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H88" s="6"/>
+      <c r="H88" s="4"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="B89" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="C89" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="D89" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="E89" s="6" t="s">
+      <c r="E89" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F89" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G89" s="6" t="s">
+      <c r="F89" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G89" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H89" s="6"/>
+      <c r="H89" s="4"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C90" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D90" s="6" t="s">
+      <c r="D90" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="E90" s="6" t="s">
+      <c r="E90" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F90" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G90" s="6" t="s">
+      <c r="F90" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G90" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H90" s="6"/>
+      <c r="H90" s="4"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D91" s="6" t="s">
+      <c r="D91" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="E91" s="6" t="s">
+      <c r="E91" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F91" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G91" s="6" t="s">
+      <c r="F91" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G91" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="H91" s="6"/>
+      <c r="H91" s="4"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="C92" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D92" s="6" t="s">
+      <c r="D92" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="E92" s="6" t="s">
+      <c r="E92" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F92" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G92" s="6" t="s">
+      <c r="F92" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G92" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H92" s="6"/>
+      <c r="H92" s="4"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C93" s="6" t="s">
+      <c r="C93" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="D93" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="E93" s="6" t="s">
+      <c r="E93" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F93" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G93" s="6" t="s">
+      <c r="F93" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G93" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H93" s="6"/>
+      <c r="H93" s="4"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="C94" s="6" t="s">
+      <c r="C94" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="D94" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="E94" s="6" t="s">
+      <c r="E94" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G94" s="6" t="s">
+      <c r="F94" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G94" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H94" s="6"/>
+      <c r="H94" s="4"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B95" s="6" t="s">
+      <c r="B95" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C95" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D95" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="E95" s="6" t="s">
+      <c r="E95" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F95" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G95" s="6" t="s">
+      <c r="F95" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G95" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H95" s="6"/>
+      <c r="H95" s="4"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B96" s="6" t="s">
+      <c r="B96" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D96" s="6" t="s">
+      <c r="D96" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="E96" s="6" t="s">
+      <c r="E96" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F96" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G96" s="6" t="s">
+      <c r="F96" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G96" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H96" s="6"/>
+      <c r="H96" s="4"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="B97" s="6" t="s">
+      <c r="B97" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C97" s="6" t="s">
+      <c r="C97" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="E97" s="6" t="s">
+      <c r="E97" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F97" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G97" s="6" t="s">
+      <c r="F97" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H97" s="6"/>
+      <c r="H97" s="4"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="C98" s="6" t="s">
+      <c r="C98" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D98" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="E98" s="6" t="s">
+      <c r="E98" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F98" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G98" s="6" t="s">
+      <c r="F98" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G98" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H98" s="6"/>
+      <c r="H98" s="4"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="B99" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C99" s="6" t="s">
+      <c r="C99" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D99" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="E99" s="6" t="s">
+      <c r="E99" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F99" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G99" s="6" t="s">
+      <c r="F99" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G99" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H99" s="6"/>
+      <c r="H99" s="4"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="B100" s="6" t="s">
+      <c r="B100" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="C100" s="6" t="s">
+      <c r="C100" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="D100" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="E100" s="7" t="s">
+      <c r="E100" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="F100" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G100" s="6" t="s">
+      <c r="F100" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G100" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H100" s="6"/>
+      <c r="H100" s="4"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="6" t="s">
+      <c r="A101" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="B101" s="6" t="s">
+      <c r="B101" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="C101" s="6" t="s">
+      <c r="C101" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="D101" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="E101" s="7" t="s">
+      <c r="E101" s="5" t="s">
         <v>870</v>
       </c>
-      <c r="F101" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G101" s="6" t="s">
+      <c r="F101" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G101" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H101" s="6"/>
+      <c r="H101" s="4"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="6" t="s">
+      <c r="A102" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="C102" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D102" s="6" t="s">
+      <c r="D102" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="E102" s="7" t="s">
+      <c r="E102" s="5" t="s">
         <v>871</v>
       </c>
-      <c r="F102" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G102" s="6" t="s">
+      <c r="F102" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G102" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H102" s="6"/>
+      <c r="H102" s="4"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="6" t="s">
+      <c r="A103" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="B103" s="6" t="s">
+      <c r="B103" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="C103" s="6" t="s">
+      <c r="C103" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="D103" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="E103" s="6" t="s">
+      <c r="E103" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F103" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G103" s="6" t="s">
+      <c r="F103" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G103" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="H103" s="6"/>
+      <c r="H103" s="4"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="11" t="s">
+      <c r="A104" s="4" t="s">
         <v>886</v>
       </c>
-      <c r="B104" s="11" t="s">
+      <c r="B104" s="4" t="s">
         <v>887</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C104" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D104" s="11" t="s">
+      <c r="D104" s="4" t="s">
         <v>888</v>
       </c>
-      <c r="E104" s="12" t="s">
+      <c r="E104" s="5" t="s">
         <v>917</v>
       </c>
-      <c r="F104" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="G104" s="11" t="s">
+      <c r="F104" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G104" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="H104" s="11" t="s">
+      <c r="H104" s="4" t="s">
         <v>893</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="11" t="s">
+      <c r="A105" s="4" t="s">
         <v>889</v>
       </c>
-      <c r="B105" s="11" t="s">
+      <c r="B105" s="4" t="s">
         <v>890</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C105" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D105" s="11" t="s">
+      <c r="D105" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="E105" s="11" t="s">
+      <c r="E105" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F105" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="G105" s="11" t="s">
+      <c r="F105" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G105" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="H105" s="11" t="s">
+      <c r="H105" s="4" t="s">
         <v>893</v>
       </c>
     </row>
@@ -5762,7 +5758,7 @@
     <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
     <col min="3" max="3" width="75.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="38.140625" customWidth="1"/>
     <col min="8" max="8" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
@@ -5777,7 +5773,7 @@
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="11" t="s">
         <v>342</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -5803,7 +5799,7 @@
       <c r="C2" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="9">
         <v>120000000</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -5827,7 +5823,7 @@
       <c r="C3" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="9">
         <v>120000000</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -5851,7 +5847,7 @@
       <c r="C4" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="9">
         <v>100000000</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -5875,7 +5871,7 @@
       <c r="C5" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="9">
         <v>90000000</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -5899,7 +5895,7 @@
       <c r="C6" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="9">
         <v>14000000</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -5923,7 +5919,7 @@
       <c r="C7" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="9">
         <v>260000000</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -5947,7 +5943,7 @@
       <c r="C8" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="9">
         <v>45000000</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -5971,7 +5967,7 @@
       <c r="C9" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="9">
         <v>5000000</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -5995,7 +5991,7 @@
       <c r="C10" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -6019,7 +6015,7 @@
       <c r="C11" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="9">
         <v>50000000</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -6043,7 +6039,7 @@
       <c r="C12" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="9">
         <v>1600000</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -6067,7 +6063,7 @@
       <c r="C13" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="9">
         <v>28000000</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -6091,7 +6087,7 @@
       <c r="C14" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="9">
         <v>31000000</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -6115,7 +6111,7 @@
       <c r="C15" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="9">
         <v>35000000</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -6139,7 +6135,7 @@
       <c r="C16" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="9">
         <v>115000000</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -6163,7 +6159,7 @@
       <c r="C17" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="9">
         <v>80000000</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -6187,7 +6183,7 @@
       <c r="C18" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -6211,7 +6207,7 @@
       <c r="C19" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="9">
         <v>57700000</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -6235,7 +6231,7 @@
       <c r="C20" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="9">
         <v>31000000</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -6259,7 +6255,7 @@
       <c r="C21" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="9">
         <v>14000000</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -6283,7 +6279,7 @@
       <c r="C22" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="9">
         <v>9300000</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -6307,7 +6303,7 @@
       <c r="C23" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="9">
         <v>1200000</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -6331,7 +6327,7 @@
       <c r="C24" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="9">
         <v>100000000</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -6355,7 +6351,7 @@
       <c r="C25" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="9">
         <v>7700000</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -6379,7 +6375,7 @@
       <c r="C26" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="9">
         <v>20000000</v>
       </c>
       <c r="E26" s="2" t="s">
@@ -6403,7 +6399,7 @@
       <c r="C27" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="9">
         <v>15000000</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -6427,7 +6423,7 @@
       <c r="C28" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="9">
         <v>142000000</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -6451,7 +6447,7 @@
       <c r="C29" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="9">
         <v>17500000</v>
       </c>
       <c r="E29" s="2" t="s">
@@ -6475,7 +6471,7 @@
       <c r="C30" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="9">
         <v>7300000</v>
       </c>
       <c r="E30" s="2" t="s">
@@ -6499,7 +6495,7 @@
       <c r="C31" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="9">
         <v>11000000</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -6523,7 +6519,7 @@
       <c r="C32" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="9">
         <v>42000000</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -6547,7 +6543,7 @@
       <c r="C33" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="9">
         <v>13600000</v>
       </c>
       <c r="E33" s="2" t="s">
@@ -6571,7 +6567,7 @@
       <c r="C34" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="9">
         <v>12700000</v>
       </c>
       <c r="E34" s="2" t="s">
@@ -6595,7 +6591,7 @@
       <c r="C35" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="9">
         <v>2000000</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -6619,7 +6615,7 @@
       <c r="C36" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E36" s="2" t="s">
@@ -6643,7 +6639,7 @@
       <c r="C37" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="9">
         <v>2300000</v>
       </c>
       <c r="E37" s="2" t="s">
@@ -6667,7 +6663,7 @@
       <c r="C38" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="9">
         <v>15000000</v>
       </c>
       <c r="E38" s="2" t="s">
@@ -6691,7 +6687,7 @@
       <c r="C39" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E39" s="2" t="s">
@@ -6715,7 +6711,7 @@
       <c r="C40" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="9">
         <v>100000000</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -6739,7 +6735,7 @@
       <c r="C41" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -6763,7 +6759,7 @@
       <c r="C42" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="9">
         <v>175000000</v>
       </c>
       <c r="E42" s="2" t="s">
@@ -6787,7 +6783,7 @@
       <c r="C43" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="9">
         <v>200000000</v>
       </c>
       <c r="E43" s="2" t="s">
@@ -6811,7 +6807,7 @@
       <c r="C44" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="9">
         <v>40000000</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -6835,7 +6831,7 @@
       <c r="C45" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="9">
         <v>11700000</v>
       </c>
       <c r="E45" s="2" t="s">
@@ -6859,7 +6855,7 @@
       <c r="C46" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="9">
         <v>65000000</v>
       </c>
       <c r="E46" s="2" t="s">
@@ -6883,7 +6879,7 @@
       <c r="C47" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="9">
         <v>53000000</v>
       </c>
       <c r="E47" s="2" t="s">
@@ -6907,7 +6903,7 @@
       <c r="C48" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="9">
         <v>120000000</v>
       </c>
       <c r="E48" s="2" t="s">
@@ -6931,7 +6927,7 @@
       <c r="C49" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="9">
         <v>5000000</v>
       </c>
       <c r="E49" s="2" t="s">
@@ -6955,7 +6951,7 @@
       <c r="C50" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="9">
         <v>7000000</v>
       </c>
       <c r="E50" s="2" t="s">
@@ -6979,7 +6975,7 @@
       <c r="C51" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="9">
         <v>17780000</v>
       </c>
       <c r="E51" s="2" t="s">
@@ -7003,7 +6999,7 @@
       <c r="C52" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="9">
         <v>24000000</v>
       </c>
       <c r="E52" s="2" t="s">
@@ -7027,7 +7023,7 @@
       <c r="C53" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="9">
         <v>65000000</v>
       </c>
       <c r="E53" s="2" t="s">
@@ -7051,7 +7047,7 @@
       <c r="C54" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="9">
         <v>175000000</v>
       </c>
       <c r="E54" s="2" t="s">
@@ -7075,7 +7071,7 @@
       <c r="C55" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="9">
         <v>13000000</v>
       </c>
       <c r="E55" s="2" t="s">
@@ -7099,7 +7095,7 @@
       <c r="C56" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="9">
         <v>10900000</v>
       </c>
       <c r="E56" s="2" t="s">
@@ -7123,7 +7119,7 @@
       <c r="C57" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="9">
         <v>25000000</v>
       </c>
       <c r="E57" s="2" t="s">
@@ -7147,7 +7143,7 @@
       <c r="C58" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="9">
         <v>83000000</v>
       </c>
       <c r="E58" s="2" t="s">
@@ -7171,7 +7167,7 @@
       <c r="C59" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="9">
         <v>30000000</v>
       </c>
       <c r="E59" s="2" t="s">
@@ -7195,7 +7191,7 @@
       <c r="C60" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="9">
         <v>5200000</v>
       </c>
       <c r="E60" s="2" t="s">
@@ -7219,7 +7215,7 @@
       <c r="C61" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="9">
         <v>100000000</v>
       </c>
       <c r="E61" s="2" t="s">
@@ -7243,7 +7239,7 @@
       <c r="C62" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="9">
         <v>1700000</v>
       </c>
       <c r="E62" s="2" t="s">
@@ -7267,7 +7263,7 @@
       <c r="C63" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D63" s="9">
         <v>200000000</v>
       </c>
       <c r="E63" s="2" t="s">
@@ -7291,7 +7287,7 @@
       <c r="C64" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="9">
         <v>38000000</v>
       </c>
       <c r="E64" s="2" t="s">
@@ -7315,7 +7311,7 @@
       <c r="C65" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D65" s="9">
         <v>31000000</v>
       </c>
       <c r="E65" s="2" t="s">
@@ -7339,7 +7335,7 @@
       <c r="C66" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="9">
         <v>2000000</v>
       </c>
       <c r="E66" s="2" t="s">
@@ -7363,7 +7359,7 @@
       <c r="C67" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67" s="9">
         <v>3000000</v>
       </c>
       <c r="E67" s="2" t="s">
@@ -7387,7 +7383,7 @@
       <c r="C68" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68" s="9">
         <v>7500000</v>
       </c>
       <c r="E68" s="2" t="s">
@@ -7411,7 +7407,7 @@
       <c r="C69" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D69" s="9">
         <v>30000000</v>
       </c>
       <c r="E69" s="2" t="s">
@@ -7435,7 +7431,7 @@
       <c r="C70" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70" s="9">
         <v>11500000</v>
       </c>
       <c r="E70" s="2" t="s">
@@ -7459,7 +7455,7 @@
       <c r="C71" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D71" s="9">
         <v>15000000</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -7483,7 +7479,7 @@
       <c r="C72" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="9">
         <v>35000000</v>
       </c>
       <c r="E72" s="2" t="s">
@@ -7507,7 +7503,7 @@
       <c r="C73" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73" s="9">
         <v>9000000</v>
       </c>
       <c r="E73" s="2" t="s">
@@ -7531,7 +7527,7 @@
       <c r="C74" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E74" s="2" t="s">
@@ -7555,7 +7551,7 @@
       <c r="C75" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D75" s="9">
         <v>35000000</v>
       </c>
       <c r="E75" s="2" t="s">
@@ -7579,7 +7575,7 @@
       <c r="C76" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="9">
         <v>10000000</v>
       </c>
       <c r="E76" s="2" t="s">
@@ -7603,7 +7599,7 @@
       <c r="C77" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E77" s="2" t="s">
@@ -7627,7 +7623,7 @@
       <c r="C78" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D78" s="9">
         <v>14400000</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -7651,7 +7647,7 @@
       <c r="C79" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="D79" s="3">
+      <c r="D79" s="9">
         <v>6000000</v>
       </c>
       <c r="E79" s="2" t="s">
@@ -7675,7 +7671,7 @@
       <c r="C80" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="D80" s="3">
+      <c r="D80" s="9">
         <v>25000000</v>
       </c>
       <c r="E80" s="2" t="s">
@@ -7699,7 +7695,7 @@
       <c r="C81" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="9">
         <v>2000000</v>
       </c>
       <c r="E81" s="2" t="s">
@@ -7723,7 +7719,7 @@
       <c r="C82" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D82" s="9">
         <v>14300000</v>
       </c>
       <c r="E82" s="2" t="s">
@@ -7747,7 +7743,7 @@
       <c r="C83" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="9">
         <v>3175000</v>
       </c>
       <c r="E83" s="2" t="s">
@@ -7771,7 +7767,7 @@
       <c r="C84" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D84" s="9">
         <v>1200000</v>
       </c>
       <c r="E84" s="2" t="s">
@@ -7795,7 +7791,7 @@
       <c r="C85" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="D85" s="3">
+      <c r="D85" s="9">
         <v>1270000</v>
       </c>
       <c r="E85" s="2" t="s">
@@ -7819,7 +7815,7 @@
       <c r="C86" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="D86" s="3">
+      <c r="D86" s="9">
         <v>20000000</v>
       </c>
       <c r="E86" s="2" t="s">
@@ -7843,7 +7839,7 @@
       <c r="C87" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="D87" s="3">
+      <c r="D87" s="9">
         <v>200000</v>
       </c>
       <c r="E87" s="2" t="s">
@@ -7867,7 +7863,7 @@
       <c r="C88" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="D88" s="3">
+      <c r="D88" s="9">
         <v>13500000</v>
       </c>
       <c r="E88" s="2" t="s">
@@ -7891,7 +7887,7 @@
       <c r="C89" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="9">
         <v>10000000</v>
       </c>
       <c r="E89" s="2" t="s">
@@ -7915,7 +7911,7 @@
       <c r="C90" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="D90" s="3">
+      <c r="D90" s="9">
         <v>42000000</v>
       </c>
       <c r="E90" s="2" t="s">
@@ -7939,7 +7935,7 @@
       <c r="C91" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="9">
         <v>45000000</v>
       </c>
       <c r="E91" s="2" t="s">
@@ -7963,7 +7959,7 @@
       <c r="C92" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D92" s="9">
         <v>4500000</v>
       </c>
       <c r="E92" s="2" t="s">
@@ -7987,7 +7983,7 @@
       <c r="C93" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D93" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E93" s="2" t="s">
@@ -8011,7 +8007,7 @@
       <c r="C94" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="9">
         <v>900000</v>
       </c>
       <c r="E94" s="2" t="s">
@@ -8035,7 +8031,7 @@
       <c r="C95" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="D95" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E95" s="2" t="s">
@@ -8059,7 +8055,7 @@
       <c r="C96" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="9">
         <v>36100000</v>
       </c>
       <c r="E96" s="2" t="s">
@@ -8083,7 +8079,7 @@
       <c r="C97" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="D97" s="3">
+      <c r="D97" s="9">
         <v>4000000</v>
       </c>
       <c r="E97" s="2" t="s">
@@ -8107,7 +8103,7 @@
       <c r="C98" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="D98" s="3">
+      <c r="D98" s="9">
         <v>2500000</v>
       </c>
       <c r="E98" s="2" t="s">
@@ -8131,7 +8127,7 @@
       <c r="C99" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="D99" s="3">
+      <c r="D99" s="9">
         <v>2500000</v>
       </c>
       <c r="E99" s="2" t="s">
@@ -8155,7 +8151,7 @@
       <c r="C100" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="9">
         <v>4500000</v>
       </c>
       <c r="E100" s="2" t="s">
@@ -8179,7 +8175,7 @@
       <c r="C101" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="D101" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E101" s="2" t="s">
@@ -8203,7 +8199,7 @@
       <c r="C102" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="D102" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E102" s="2" t="s">
@@ -8227,7 +8223,7 @@
       <c r="C103" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="D103" s="3">
+      <c r="D103" s="9">
         <v>1524000</v>
       </c>
       <c r="E103" s="2" t="s">
@@ -8251,7 +8247,7 @@
       <c r="C104" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="D104" s="3">
+      <c r="D104" s="9">
         <v>17900000</v>
       </c>
       <c r="E104" s="2" t="s">
@@ -8275,7 +8271,7 @@
       <c r="C105" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="D105" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E105" s="2" t="s">
@@ -8299,7 +8295,7 @@
       <c r="C106" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="D106" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E106" s="2" t="s">
@@ -8323,7 +8319,7 @@
       <c r="C107" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="D107" s="3">
+      <c r="D107" s="9">
         <v>6000000</v>
       </c>
       <c r="E107" s="2" t="s">
@@ -8347,7 +8343,7 @@
       <c r="C108" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="D108" s="3">
+      <c r="D108" s="9">
         <v>20000000</v>
       </c>
       <c r="E108" s="2" t="s">
@@ -8371,7 +8367,7 @@
       <c r="C109" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="D109" s="3">
+      <c r="D109" s="9">
         <v>16000000</v>
       </c>
       <c r="E109" s="2" t="s">
@@ -8395,7 +8391,7 @@
       <c r="C110" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="D110" s="3">
+      <c r="D110" s="9">
         <v>1180000</v>
       </c>
       <c r="E110" s="2" t="s">
@@ -8419,7 +8415,7 @@
       <c r="C111" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="D111" s="3">
+      <c r="D111" s="9">
         <v>6000000</v>
       </c>
       <c r="E111" s="2" t="s">
@@ -8443,7 +8439,7 @@
       <c r="C112" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="D112" s="3">
+      <c r="D112" s="9">
         <v>7909999</v>
       </c>
       <c r="E112" s="2" t="s">
@@ -8467,7 +8463,7 @@
       <c r="C113" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="D113" s="3">
+      <c r="D113" s="9">
         <v>29400000</v>
       </c>
       <c r="E113" s="2" t="s">
@@ -8491,7 +8487,7 @@
       <c r="C114" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="D114" s="3">
+      <c r="D114" s="9">
         <v>370000</v>
       </c>
       <c r="E114" s="2" t="s">
@@ -8515,7 +8511,7 @@
       <c r="C115" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="D115" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E115" s="2" t="s">
@@ -8539,7 +8535,7 @@
       <c r="C116" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="D116" s="3">
+      <c r="D116" s="9">
         <v>7500000</v>
       </c>
       <c r="E116" s="2" t="s">
@@ -8563,7 +8559,7 @@
       <c r="C117" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="D117" s="3">
+      <c r="D117" s="9">
         <v>1800000</v>
       </c>
       <c r="E117" s="2" t="s">
@@ -8587,7 +8583,7 @@
       <c r="C118" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D118" s="3">
+      <c r="D118" s="9">
         <v>2300000</v>
       </c>
       <c r="E118" s="2" t="s">
@@ -8611,7 +8607,7 @@
       <c r="C119" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D119" s="3">
+      <c r="D119" s="9">
         <v>50000000</v>
       </c>
       <c r="E119" s="2" t="s">
@@ -8635,7 +8631,7 @@
       <c r="C120" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="D120" s="3">
+      <c r="D120" s="9">
         <v>2000000</v>
       </c>
       <c r="E120" s="2" t="s">
@@ -8659,7 +8655,7 @@
       <c r="C121" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="D121" s="4" t="s">
+      <c r="D121" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E121" s="2" t="s">
@@ -8683,7 +8679,7 @@
       <c r="C122" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="D122" s="3">
+      <c r="D122" s="9">
         <v>450000000</v>
       </c>
       <c r="E122" s="2" t="s">
@@ -8707,7 +8703,7 @@
       <c r="C123" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="D123" s="3">
+      <c r="D123" s="9">
         <v>27300000</v>
       </c>
       <c r="E123" s="2" t="s">
@@ -8731,7 +8727,7 @@
       <c r="C124" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="D124" s="3">
+      <c r="D124" s="9">
         <v>11500000</v>
       </c>
       <c r="E124" s="2" t="s">
@@ -8755,7 +8751,7 @@
       <c r="C125" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="D125" s="3">
+      <c r="D125" s="9">
         <v>30000000</v>
       </c>
       <c r="E125" s="2" t="s">
@@ -8779,7 +8775,7 @@
       <c r="C126" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="D126" s="3">
+      <c r="D126" s="9">
         <v>20000000</v>
       </c>
       <c r="E126" s="2" t="s">
@@ -8803,7 +8799,7 @@
       <c r="C127" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="D127" s="3">
+      <c r="D127" s="9">
         <v>10000000</v>
       </c>
       <c r="E127" s="2" t="s">
@@ -8827,7 +8823,7 @@
       <c r="C128" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="D128" s="3">
+      <c r="D128" s="9">
         <v>56000000</v>
       </c>
       <c r="E128" s="2" t="s">
@@ -8851,7 +8847,7 @@
       <c r="C129" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="D129" s="3">
+      <c r="D129" s="9">
         <v>12000000</v>
       </c>
       <c r="E129" s="2" t="s">
@@ -8875,7 +8871,7 @@
       <c r="C130" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="D130" s="3">
+      <c r="D130" s="9">
         <v>20000000</v>
       </c>
       <c r="E130" s="2" t="s">
@@ -8899,7 +8895,7 @@
       <c r="C131" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="D131" s="3">
+      <c r="D131" s="9">
         <v>27500000</v>
       </c>
       <c r="E131" s="2" t="s">
@@ -8923,7 +8919,7 @@
       <c r="C132" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="D132" s="3">
+      <c r="D132" s="9">
         <v>4700000</v>
       </c>
       <c r="E132" s="2" t="s">
@@ -8947,7 +8943,7 @@
       <c r="C133" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="D133" s="3">
+      <c r="D133" s="9">
         <v>14000000</v>
       </c>
       <c r="E133" s="2" t="s">
@@ -8971,7 +8967,7 @@
       <c r="C134" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="D134" s="3">
+      <c r="D134" s="9">
         <v>250000</v>
       </c>
       <c r="E134" s="2" t="s">
@@ -8995,7 +8991,7 @@
       <c r="C135" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="D135" s="3">
+      <c r="D135" s="9">
         <v>1200000</v>
       </c>
       <c r="E135" s="2" t="s">
@@ -9019,7 +9015,7 @@
       <c r="C136" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="D136" s="3">
+      <c r="D136" s="9">
         <v>11000000</v>
       </c>
       <c r="E136" s="2" t="s">
@@ -9043,7 +9039,7 @@
       <c r="C137" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="D137" s="3">
+      <c r="D137" s="9">
         <v>40000000</v>
       </c>
       <c r="E137" s="2" t="s">
@@ -9067,7 +9063,7 @@
       <c r="C138" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="D138" s="4" t="s">
+      <c r="D138" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E138" s="2" t="s">
@@ -9091,7 +9087,7 @@
       <c r="C139" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="D139" s="3">
+      <c r="D139" s="9">
         <v>16000000</v>
       </c>
       <c r="E139" s="2" t="s">
@@ -9115,7 +9111,7 @@
       <c r="C140" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="D140" s="4" t="s">
+      <c r="D140" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E140" s="2" t="s">
@@ -9139,7 +9135,7 @@
       <c r="C141" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="D141" s="3">
+      <c r="D141" s="9">
         <v>2500000</v>
       </c>
       <c r="E141" s="2" t="s">
@@ -9163,7 +9159,7 @@
       <c r="C142" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="D142" s="3">
+      <c r="D142" s="9">
         <v>12000000</v>
       </c>
       <c r="E142" s="2" t="s">
@@ -9187,7 +9183,7 @@
       <c r="C143" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="D143" s="3">
+      <c r="D143" s="9">
         <v>1440000</v>
       </c>
       <c r="E143" s="2" t="s">
@@ -9211,7 +9207,7 @@
       <c r="C144" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="D144" s="3">
+      <c r="D144" s="9">
         <v>2857500</v>
       </c>
       <c r="E144" s="2" t="s">
@@ -9235,7 +9231,7 @@
       <c r="C145" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="D145" s="3">
+      <c r="D145" s="9">
         <v>2300000</v>
       </c>
       <c r="E145" s="2" t="s">
@@ -9259,7 +9255,7 @@
       <c r="C146" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="D146" s="3">
+      <c r="D146" s="9">
         <v>35000000</v>
       </c>
       <c r="E146" s="2" t="s">
@@ -9283,7 +9279,7 @@
       <c r="C147" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="D147" s="3">
+      <c r="D147" s="9">
         <v>50000000</v>
       </c>
       <c r="E147" s="2" t="s">
@@ -9307,7 +9303,7 @@
       <c r="C148" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="D148" s="3">
+      <c r="D148" s="9">
         <v>8200000</v>
       </c>
       <c r="E148" s="2" t="s">
@@ -9331,7 +9327,7 @@
       <c r="C149" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="D149" s="3">
+      <c r="D149" s="9">
         <v>4500000</v>
       </c>
       <c r="E149" s="2" t="s">
@@ -9355,7 +9351,7 @@
       <c r="C150" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="D150" s="3">
+      <c r="D150" s="9">
         <v>75000000</v>
       </c>
       <c r="E150" s="2" t="s">
@@ -9379,7 +9375,7 @@
       <c r="C151" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="D151" s="3">
+      <c r="D151" s="9">
         <v>24000000</v>
       </c>
       <c r="E151" s="2" t="s">
@@ -9403,7 +9399,7 @@
       <c r="C152" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="D152" s="3">
+      <c r="D152" s="9">
         <v>16000000</v>
       </c>
       <c r="E152" s="2" t="s">
@@ -9427,7 +9423,7 @@
       <c r="C153" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="D153" s="3">
+      <c r="D153" s="9">
         <v>8000000</v>
       </c>
       <c r="E153" s="2" t="s">
@@ -9451,7 +9447,7 @@
       <c r="C154" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="D154" s="3">
+      <c r="D154" s="9">
         <v>1304000</v>
       </c>
       <c r="E154" s="2" t="s">
@@ -9475,7 +9471,7 @@
       <c r="C155" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="D155" s="3">
+      <c r="D155" s="9">
         <v>400000</v>
       </c>
       <c r="E155" s="2" t="s">
@@ -9499,7 +9495,7 @@
       <c r="C156" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="D156" s="3">
+      <c r="D156" s="9">
         <v>7000000</v>
       </c>
       <c r="E156" s="2" t="s">
@@ -9523,7 +9519,7 @@
       <c r="C157" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="D157" s="3">
+      <c r="D157" s="9">
         <v>67000000</v>
       </c>
       <c r="E157" s="2" t="s">
@@ -9547,7 +9543,7 @@
       <c r="C158" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="D158" s="3">
+      <c r="D158" s="9">
         <v>10000000</v>
       </c>
       <c r="E158" s="2" t="s">
@@ -9571,7 +9567,7 @@
       <c r="C159" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="D159" s="3">
+      <c r="D159" s="9">
         <v>120000000</v>
       </c>
       <c r="E159" s="2" t="s">
@@ -9595,7 +9591,7 @@
       <c r="C160" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="D160" s="3">
+      <c r="D160" s="9">
         <v>85000000</v>
       </c>
       <c r="E160" s="2" t="s">
@@ -9619,7 +9615,7 @@
       <c r="C161" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="D161" s="3">
+      <c r="D161" s="9">
         <v>162500000</v>
       </c>
       <c r="E161" s="2" t="s">
@@ -9643,7 +9639,7 @@
       <c r="C162" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="D162" s="3">
+      <c r="D162" s="9">
         <v>60000000</v>
       </c>
       <c r="E162" s="2" t="s">
@@ -9667,7 +9663,7 @@
       <c r="C163" s="2" t="s">
         <v>812</v>
       </c>
-      <c r="D163" s="3">
+      <c r="D163" s="9">
         <v>238000000</v>
       </c>
       <c r="E163" s="2" t="s">
@@ -9691,7 +9687,7 @@
       <c r="C164" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="D164" s="3">
+      <c r="D164" s="9">
         <v>8000000</v>
       </c>
       <c r="E164" s="2" t="s">
@@ -9715,7 +9711,7 @@
       <c r="C165" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="D165" s="3">
+      <c r="D165" s="9">
         <v>316700000</v>
       </c>
       <c r="E165" s="2" t="s">
@@ -9739,7 +9735,7 @@
       <c r="C166" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="D166" s="3">
+      <c r="D166" s="9">
         <v>170000000</v>
       </c>
       <c r="E166" s="2" t="s">
@@ -9763,7 +9759,7 @@
       <c r="C167" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="D167" s="3">
+      <c r="D167" s="9">
         <v>130000000</v>
       </c>
       <c r="E167" s="2" t="s">
@@ -9787,7 +9783,7 @@
       <c r="C168" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="D168" s="3">
+      <c r="D168" s="9">
         <v>110000000</v>
       </c>
       <c r="E168" s="2" t="s">
@@ -9811,7 +9807,7 @@
       <c r="C169" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="D169" s="3">
+      <c r="D169" s="9">
         <v>65000000</v>
       </c>
       <c r="E169" s="2" t="s">
@@ -9835,7 +9831,7 @@
       <c r="C170" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="D170" s="3">
+      <c r="D170" s="9">
         <v>104000000</v>
       </c>
       <c r="E170" s="2" t="s">
@@ -9859,7 +9855,7 @@
       <c r="C171" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="D171" s="3">
+      <c r="D171" s="9">
         <v>16000000</v>
       </c>
       <c r="E171" s="2" t="s">
@@ -9883,7 +9879,7 @@
       <c r="C172" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="D172" s="3">
+      <c r="D172" s="9">
         <v>1270000</v>
       </c>
       <c r="E172" s="2" t="s">
@@ -9907,7 +9903,7 @@
       <c r="C173" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D173" s="3">
+      <c r="D173" s="9">
         <v>50000000</v>
       </c>
       <c r="E173" s="2" t="s">
@@ -9931,7 +9927,7 @@
       <c r="C174" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D174" s="3">
+      <c r="D174" s="9">
         <v>323850</v>
       </c>
       <c r="E174" s="2" t="s">
@@ -9955,7 +9951,7 @@
       <c r="C175" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="D175" s="4" t="s">
+      <c r="D175" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E175" s="2" t="s">
@@ -9979,7 +9975,7 @@
       <c r="C176" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="D176" s="4" t="s">
+      <c r="D176" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E176" s="2" t="s">
@@ -10003,7 +9999,7 @@
       <c r="C177" s="2" t="s">
         <v>851</v>
       </c>
-      <c r="D177" s="14">
+      <c r="D177" s="9">
         <v>2800000</v>
       </c>
       <c r="E177" s="2" t="s">
@@ -10027,7 +10023,7 @@
       <c r="C178" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="D178" s="14">
+      <c r="D178" s="9">
         <v>85000000</v>
       </c>
       <c r="E178" s="2" t="s">
@@ -10051,7 +10047,7 @@
       <c r="C179" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="D179" s="14">
+      <c r="D179" s="9">
         <v>100000000</v>
       </c>
       <c r="E179" s="2" t="s">
@@ -10075,7 +10071,7 @@
       <c r="C180" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="D180" s="14">
+      <c r="D180" s="9">
         <v>4875000</v>
       </c>
       <c r="E180" s="2" t="s">
@@ -10099,7 +10095,7 @@
       <c r="C181" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="D181" s="14">
+      <c r="D181" s="9">
         <v>5000000</v>
       </c>
       <c r="E181" s="2" t="s">
@@ -10123,7 +10119,7 @@
       <c r="C182" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="D182" s="14">
+      <c r="D182" s="9">
         <v>90000000</v>
       </c>
       <c r="E182" s="2" t="s">
@@ -10147,7 +10143,7 @@
       <c r="C183" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="D183" s="14">
+      <c r="D183" s="9">
         <v>10000000</v>
       </c>
       <c r="E183" s="2" t="s">
@@ -10371,13 +10367,13 @@
       <c r="D2" t="s">
         <v>878</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="3">
         <v>17000000</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G2" s="9">
+      <c r="F2" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G2" s="7">
         <v>45898</v>
       </c>
     </row>
@@ -10394,151 +10390,151 @@
       <c r="D3" t="s">
         <v>880</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="3">
         <v>75000000</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G3" s="9">
+      <c r="F3" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G3" s="7">
         <v>45868</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>905</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>876</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>906</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>907</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>872</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="7">
         <v>45658</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>908</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>876</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>909</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>907</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="8" t="s">
         <v>919</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>872</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="7">
         <v>45717</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>910</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>876</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>911</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>907</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="8" t="s">
         <v>920</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>873</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="7">
         <v>45809</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>718</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>876</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>912</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>907</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="8" t="s">
         <v>921</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="G7" s="9">
+      <c r="F7" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="G7" s="7">
         <v>45839</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>913</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>876</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>914</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>907</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="8" t="s">
         <v>922</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="G8" s="9">
+      <c r="F8" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="G8" s="7">
         <v>45870</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>817</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>876</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="8" t="s">
         <v>923</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G9" s="9">
+      <c r="F9" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G9" s="7">
         <v>45901</v>
       </c>
     </row>

--- a/data/MedTech_YTD_Standardized.xlsx
+++ b/data/MedTech_YTD_Standardized.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beacononehcp-my.sharepoint.com/personal/hannah_peric_beacononehcp_com/Documents/Documents/medtech-dashboard/Medtech-Dashboard-M-A/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beacononehcp-my.sharepoint.com/personal/hannah_peric_beacononehcp_com/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="86" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{333F7B8D-B0BB-4698-A44B-B355772C16C5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD M&amp;A Activity" sheetId="1" r:id="rId1"/>

--- a/data/MedTech_YTD_Standardized.xlsx
+++ b/data/MedTech_YTD_Standardized.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beacononehcp-my.sharepoint.com/personal/hannah_peric_beacononehcp_com/Documents/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beacononehcp-my.sharepoint.com/personal/hannah_peric_beacononehcp_com/Documents/Documents/medtech-dashboard/Medtech-Dashboard-M-A/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{333F7B8D-B0BB-4698-A44B-B355772C16C5}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8437E4D-B5B8-4C39-A7F4-F05CB8740D97}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,10 @@
     <sheet name="YTD Investment Activity" sheetId="2" r:id="rId2"/>
     <sheet name="YTD IPO" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'YTD Investment Activity'!$A$1:$H$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YTD M&amp;A Activity'!$A$1:$H$105</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -915,9 +919,6 @@
     <t>Acquisition of bioenvelopes designed to protect patients with implantable devices.</t>
   </si>
   <si>
-    <t>$88 million</t>
-  </si>
-  <si>
     <t>PolyCraft Tech</t>
   </si>
   <si>
@@ -2794,16 +2795,22 @@
   </si>
   <si>
     <t>$364000000</t>
+  </si>
+  <si>
+    <t>$88000000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2817,6 +2824,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2857,8 +2871,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2870,7 +2885,6 @@
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2880,18 +2894,20 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -3203,6 +3219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3237,7 +3254,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3253,18 +3270,18 @@
       <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="10" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
@@ -3281,7 +3298,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>12</v>
@@ -3301,18 +3318,18 @@
       <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
@@ -3329,14 +3346,14 @@
         <v>16</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
@@ -3353,14 +3370,14 @@
         <v>16</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>27</v>
       </c>
@@ -3377,14 +3394,14 @@
         <v>16</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>30</v>
       </c>
@@ -3401,14 +3418,14 @@
         <v>16</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
@@ -3425,14 +3442,14 @@
         <v>16</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>36</v>
       </c>
@@ -3449,14 +3466,14 @@
         <v>16</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>39</v>
       </c>
@@ -3473,14 +3490,14 @@
         <v>16</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>42</v>
       </c>
@@ -3497,14 +3514,14 @@
         <v>16</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>45</v>
       </c>
@@ -3521,14 +3538,14 @@
         <v>16</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>48</v>
       </c>
@@ -3545,14 +3562,14 @@
         <v>16</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>51</v>
       </c>
@@ -3569,14 +3586,14 @@
         <v>16</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>54</v>
       </c>
@@ -3593,14 +3610,14 @@
         <v>16</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>57</v>
       </c>
@@ -3617,14 +3634,14 @@
         <v>16</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>59</v>
       </c>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>60</v>
       </c>
@@ -3641,14 +3658,14 @@
         <v>16</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>59</v>
       </c>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>63</v>
       </c>
@@ -3665,14 +3682,14 @@
         <v>16</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>59</v>
       </c>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>66</v>
       </c>
@@ -3689,7 +3706,7 @@
         <v>16</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>59</v>
@@ -3709,18 +3726,18 @@
       <c r="D21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="10" t="s">
         <v>72</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>59</v>
       </c>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>73</v>
       </c>
@@ -3737,7 +3754,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>59</v>
@@ -3757,11 +3774,11 @@
       <c r="D23" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="10" t="s">
         <v>79</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>59</v>
@@ -3781,18 +3798,18 @@
       <c r="D24" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="10" t="s">
         <v>83</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>59</v>
       </c>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>84</v>
       </c>
@@ -3809,7 +3826,7 @@
         <v>16</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>59</v>
@@ -3829,18 +3846,18 @@
       <c r="D26" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="10" t="s">
         <v>90</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>92</v>
       </c>
@@ -3857,7 +3874,7 @@
         <v>16</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>91</v>
@@ -3877,18 +3894,18 @@
       <c r="D28" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="10" t="s">
         <v>98</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>91</v>
       </c>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>99</v>
       </c>
@@ -3905,14 +3922,14 @@
         <v>16</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>91</v>
       </c>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>102</v>
       </c>
@@ -3929,14 +3946,14 @@
         <v>16</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>91</v>
       </c>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>105</v>
       </c>
@@ -3953,7 +3970,7 @@
         <v>16</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>91</v>
@@ -3973,18 +3990,18 @@
       <c r="D32" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="10" t="s">
         <v>111</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>91</v>
       </c>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>112</v>
       </c>
@@ -4001,7 +4018,7 @@
         <v>16</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>91</v>
@@ -4021,18 +4038,18 @@
       <c r="D34" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="10" t="s">
         <v>119</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>91</v>
       </c>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>120</v>
       </c>
@@ -4049,7 +4066,7 @@
         <v>16</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>123</v>
@@ -4069,11 +4086,11 @@
       <c r="D36" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="10" t="s">
         <v>127</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>123</v>
@@ -4093,11 +4110,11 @@
       <c r="D37" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="10" t="s">
         <v>130</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>123</v>
@@ -4117,18 +4134,18 @@
       <c r="D38" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="10" t="s">
         <v>134</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>135</v>
       </c>
@@ -4145,14 +4162,14 @@
         <v>16</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -4169,14 +4186,14 @@
         <v>16</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>142</v>
       </c>
@@ -4193,7 +4210,7 @@
         <v>16</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>123</v>
@@ -4213,11 +4230,11 @@
       <c r="D42" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="10" t="s">
         <v>148</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>123</v>
@@ -4237,11 +4254,11 @@
       <c r="D43" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="10" t="s">
         <v>152</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>123</v>
@@ -4261,18 +4278,18 @@
       <c r="D44" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="10" t="s">
         <v>156</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H44" s="4"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>157</v>
       </c>
@@ -4289,14 +4306,14 @@
         <v>16</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H45" s="4"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>160</v>
       </c>
@@ -4313,7 +4330,7 @@
         <v>16</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>163</v>
@@ -4333,11 +4350,11 @@
       <c r="D47" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="10" t="s">
         <v>167</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>163</v>
@@ -4357,18 +4374,18 @@
       <c r="D48" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="10" t="s">
         <v>171</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>163</v>
       </c>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>172</v>
       </c>
@@ -4385,14 +4402,14 @@
         <v>16</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>163</v>
       </c>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>175</v>
       </c>
@@ -4409,14 +4426,14 @@
         <v>16</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>163</v>
       </c>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>177</v>
       </c>
@@ -4433,7 +4450,7 @@
         <v>16</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>163</v>
@@ -4453,18 +4470,18 @@
       <c r="D52" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="10" t="s">
         <v>183</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>163</v>
       </c>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>184</v>
       </c>
@@ -4481,7 +4498,7 @@
         <v>16</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>163</v>
@@ -4501,18 +4518,18 @@
       <c r="D54" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="10" t="s">
         <v>190</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>163</v>
       </c>
       <c r="H54" s="4"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>191</v>
       </c>
@@ -4529,14 +4546,14 @@
         <v>16</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>163</v>
       </c>
       <c r="H55" s="4"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>194</v>
       </c>
@@ -4553,14 +4570,14 @@
         <v>16</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>163</v>
       </c>
       <c r="H56" s="4"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>197</v>
       </c>
@@ -4577,14 +4594,14 @@
         <v>16</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>200</v>
       </c>
       <c r="H57" s="4"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>201</v>
       </c>
@@ -4601,7 +4618,7 @@
         <v>16</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>200</v>
@@ -4621,11 +4638,11 @@
       <c r="D59" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="10" t="s">
         <v>207</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>200</v>
@@ -4645,7 +4662,7 @@
       <c r="D60" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E60" s="10" t="s">
         <v>210</v>
       </c>
       <c r="F60" s="4" t="s">
@@ -4656,7 +4673,7 @@
       </c>
       <c r="H60" s="4"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>212</v>
       </c>
@@ -4693,7 +4710,7 @@
       <c r="D62" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="10" t="s">
         <v>218</v>
       </c>
       <c r="F62" s="4" t="s">
@@ -4717,7 +4734,7 @@
       <c r="D63" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="10" t="s">
         <v>222</v>
       </c>
       <c r="F63" s="4" t="s">
@@ -4730,7 +4747,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>223</v>
@@ -4741,7 +4758,7 @@
       <c r="D64" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="E64" s="10" t="s">
         <v>225</v>
       </c>
       <c r="F64" s="4" t="s">
@@ -4751,7 +4768,7 @@
         <v>215</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4767,7 +4784,7 @@
       <c r="D65" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="E65" s="10" t="s">
         <v>225</v>
       </c>
       <c r="F65" s="4" t="s">
@@ -4791,7 +4808,7 @@
       <c r="D66" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E66" s="10" t="s">
         <v>230</v>
       </c>
       <c r="F66" s="4" t="s">
@@ -4815,7 +4832,7 @@
       <c r="D67" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E67" s="10" t="s">
         <v>236</v>
       </c>
       <c r="F67" s="4" t="s">
@@ -4839,7 +4856,7 @@
       <c r="D68" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="E68" s="10" t="s">
         <v>240</v>
       </c>
       <c r="F68" s="4" t="s">
@@ -4850,7 +4867,7 @@
       </c>
       <c r="H68" s="4"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>241</v>
       </c>
@@ -4874,7 +4891,7 @@
       </c>
       <c r="H69" s="4"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>244</v>
       </c>
@@ -4898,7 +4915,7 @@
       </c>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>247</v>
       </c>
@@ -4915,14 +4932,14 @@
         <v>16</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>200</v>
       </c>
       <c r="H71" s="4"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>248</v>
       </c>
@@ -4939,14 +4956,14 @@
         <v>16</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>200</v>
       </c>
       <c r="H72" s="4"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>251</v>
       </c>
@@ -4963,14 +4980,14 @@
         <v>16</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>200</v>
       </c>
       <c r="H73" s="4"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>254</v>
       </c>
@@ -4987,14 +5004,14 @@
         <v>16</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>91</v>
       </c>
       <c r="H74" s="4"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>257</v>
       </c>
@@ -5011,16 +5028,16 @@
         <v>16</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>91</v>
       </c>
       <c r="H75" s="4"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>260</v>
@@ -5035,7 +5052,7 @@
         <v>16</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>91</v>
@@ -5055,8 +5072,8 @@
       <c r="D77" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="E77" s="5" t="s">
-        <v>868</v>
+      <c r="E77" s="10" t="s">
+        <v>867</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>264</v>
@@ -5066,7 +5083,7 @@
       </c>
       <c r="H77" s="4"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>265</v>
       </c>
@@ -5090,7 +5107,7 @@
       </c>
       <c r="H78" s="4"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>268</v>
       </c>
@@ -5114,7 +5131,7 @@
       </c>
       <c r="H79" s="4"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>271</v>
       </c>
@@ -5138,7 +5155,7 @@
       </c>
       <c r="H80" s="4"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>274</v>
       </c>
@@ -5162,7 +5179,7 @@
       </c>
       <c r="H81" s="4"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>278</v>
       </c>
@@ -5186,7 +5203,7 @@
       </c>
       <c r="H82" s="4"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>280</v>
       </c>
@@ -5210,7 +5227,7 @@
       </c>
       <c r="H83" s="4"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>283</v>
       </c>
@@ -5234,7 +5251,7 @@
       </c>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>286</v>
       </c>
@@ -5258,7 +5275,7 @@
       </c>
       <c r="H85" s="4"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>289</v>
       </c>
@@ -5282,7 +5299,7 @@
       </c>
       <c r="H86" s="4"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>292</v>
       </c>
@@ -5319,8 +5336,8 @@
       <c r="D88" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="E88" s="4" t="s">
-        <v>297</v>
+      <c r="E88" s="10" t="s">
+        <v>923</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>277</v>
@@ -5330,18 +5347,18 @@
       </c>
       <c r="H88" s="4"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>299</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>16</v>
@@ -5354,9 +5371,9 @@
       </c>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>192</v>
@@ -5365,7 +5382,7 @@
         <v>9</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>16</v>
@@ -5378,18 +5395,18 @@
       </c>
       <c r="H90" s="4"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>16</v>
@@ -5398,22 +5415,22 @@
         <v>277</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H91" s="4"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B92" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>309</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>16</v>
@@ -5426,9 +5443,9 @@
       </c>
       <c r="H92" s="4"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>46</v>
@@ -5437,7 +5454,7 @@
         <v>9</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>16</v>
@@ -5450,18 +5467,18 @@
       </c>
       <c r="H93" s="4"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B94" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>16</v>
@@ -5474,18 +5491,18 @@
       </c>
       <c r="H94" s="4"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B95" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>317</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>16</v>
@@ -5498,18 +5515,18 @@
       </c>
       <c r="H95" s="4"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B96" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>16</v>
@@ -5522,9 +5539,9 @@
       </c>
       <c r="H96" s="4"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>109</v>
@@ -5533,7 +5550,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>16</v>
@@ -5546,9 +5563,9 @@
       </c>
       <c r="H97" s="4"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>287</v>
@@ -5557,7 +5574,7 @@
         <v>9</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>16</v>
@@ -5570,18 +5587,18 @@
       </c>
       <c r="H98" s="4"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B99" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>16</v>
@@ -5596,19 +5613,19 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B100" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>869</v>
+        <v>330</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>868</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>277</v>
@@ -5620,19 +5637,19 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>333</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>870</v>
+        <v>333</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>869</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>277</v>
@@ -5644,19 +5661,19 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B102" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>336</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>871</v>
+        <v>336</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>870</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>277</v>
@@ -5666,18 +5683,18 @@
       </c>
       <c r="H102" s="4"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B103" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>339</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>16</v>
@@ -5692,42 +5709,42 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="B104" s="4" t="s">
         <v>886</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>887</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
         <v>888</v>
       </c>
-      <c r="E104" s="5" t="s">
-        <v>917</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="4" t="s">
+      <c r="B105" s="4" t="s">
         <v>889</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>890</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>16</v>
@@ -5736,13 +5753,52 @@
         <v>277</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H105" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="$1,100,000,000"/>
+        <filter val="$1,500,000,000"/>
+        <filter val="$100,000,000"/>
+        <filter val="$120,000,000"/>
+        <filter val="$130,000,000"/>
+        <filter val="$15000000"/>
+        <filter val="$152,000,000"/>
+        <filter val="$17,000,000"/>
+        <filter val="$17,500,000,000"/>
+        <filter val="$18300000000"/>
+        <filter val="$225,000,000"/>
+        <filter val="$2250000000"/>
+        <filter val="$250,000,000"/>
+        <filter val="$256,000,000"/>
+        <filter val="$30000000"/>
+        <filter val="$350,000,000"/>
+        <filter val="$4,100,000,000"/>
+        <filter val="$4,900,000,000"/>
+        <filter val="$425,000,000"/>
+        <filter val="$430,000,000"/>
+        <filter val="$497,000,000"/>
+        <filter val="$5,100,000,000"/>
+        <filter val="$517,000,000"/>
+        <filter val="$533,000,000"/>
+        <filter val="$540,000,000"/>
+        <filter val="$6,000,000"/>
+        <filter val="$664,000,000"/>
+        <filter val="$815000000"/>
+        <filter val="$85,000,000"/>
+        <filter val="$88 million"/>
+        <filter val="$88,000,000"/>
+        <filter val="$883,000,000"/>
+        <filter val="$9,000,000"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
@@ -5758,7 +5814,7 @@
     <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
     <col min="3" max="3" width="75.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="38.140625" customWidth="1"/>
     <col min="8" max="8" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
@@ -5768,16 +5824,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -5786,27 +5842,27 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="11">
+        <v>120000000</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D2" s="9">
-        <v>120000000</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
@@ -5815,22 +5871,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D3" s="9">
+      <c r="D3" s="11">
         <v>120000000</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>12</v>
@@ -5839,22 +5895,22 @@
     </row>
     <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="11">
+        <v>100000000</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D4" s="9">
-        <v>100000000</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>353</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>12</v>
@@ -5863,22 +5919,22 @@
     </row>
     <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="11">
+        <v>90000000</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="D5" s="9">
-        <v>90000000</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>12</v>
@@ -5887,22 +5943,22 @@
     </row>
     <row r="6" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="11">
+        <v>14000000</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D6" s="9">
-        <v>14000000</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>12</v>
@@ -5911,22 +5967,22 @@
     </row>
     <row r="7" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="11">
+        <v>260000000</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D7" s="9">
-        <v>260000000</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>363</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>12</v>
@@ -5935,22 +5991,22 @@
     </row>
     <row r="8" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="11">
+        <v>45000000</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="D8" s="9">
-        <v>45000000</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>366</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>12</v>
@@ -5959,22 +6015,22 @@
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="11">
+        <v>5000000</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="D9" s="9">
-        <v>5000000</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>369</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>12</v>
@@ -5983,22 +6039,22 @@
     </row>
     <row r="10" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>372</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>12</v>
@@ -6007,22 +6063,22 @@
     </row>
     <row r="11" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="11">
+        <v>50000000</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D11" s="9">
-        <v>50000000</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>12</v>
@@ -6031,22 +6087,22 @@
     </row>
     <row r="12" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="11">
+        <v>1600000</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="D12" s="9">
-        <v>1600000</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>378</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>12</v>
@@ -6055,22 +6111,22 @@
     </row>
     <row r="13" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="11">
+        <v>28000000</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D13" s="9">
-        <v>28000000</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>12</v>
@@ -6079,22 +6135,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="11">
+        <v>31000000</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D14" s="9">
-        <v>31000000</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>12</v>
@@ -6103,22 +6159,22 @@
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="11">
+        <v>35000000</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D15" s="9">
-        <v>35000000</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>387</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>12</v>
@@ -6127,22 +6183,22 @@
     </row>
     <row r="16" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="11">
+        <v>115000000</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="D16" s="9">
-        <v>115000000</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>390</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>12</v>
@@ -6151,22 +6207,22 @@
     </row>
     <row r="17" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="11">
+        <v>80000000</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D17" s="9">
-        <v>80000000</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>393</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>12</v>
@@ -6175,22 +6231,22 @@
     </row>
     <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>396</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>12</v>
@@ -6199,22 +6255,22 @@
     </row>
     <row r="19" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="11">
+        <v>57700000</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D19" s="9">
-        <v>57700000</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>399</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>59</v>
@@ -6223,22 +6279,22 @@
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="11">
+        <v>31000000</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D20" s="9">
-        <v>31000000</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>402</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>59</v>
@@ -6247,22 +6303,22 @@
     </row>
     <row r="21" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D21" s="9">
+      <c r="D21" s="11">
         <v>14000000</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>59</v>
@@ -6271,22 +6327,22 @@
     </row>
     <row r="22" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="11">
+        <v>9300000</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="D22" s="9">
-        <v>9300000</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>407</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>59</v>
@@ -6295,22 +6351,22 @@
     </row>
     <row r="23" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D23" s="9">
+      <c r="D23" s="11">
         <v>1200000</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>59</v>
@@ -6319,22 +6375,22 @@
     </row>
     <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="11">
+        <v>100000000</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D24" s="9">
-        <v>100000000</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>412</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>59</v>
@@ -6343,22 +6399,22 @@
     </row>
     <row r="25" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="11">
+        <v>7700000</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D25" s="9">
-        <v>7700000</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>415</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>59</v>
@@ -6367,22 +6423,22 @@
     </row>
     <row r="26" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D26" s="9">
+      <c r="D26" s="11">
         <v>20000000</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>59</v>
@@ -6391,22 +6447,22 @@
     </row>
     <row r="27" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="11">
+        <v>15000000</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D27" s="9">
-        <v>15000000</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>420</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>59</v>
@@ -6415,22 +6471,22 @@
     </row>
     <row r="28" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D28" s="11">
+        <v>142000000</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D28" s="9">
-        <v>142000000</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>422</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>59</v>
@@ -6439,22 +6495,22 @@
     </row>
     <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="11">
+        <v>17500000</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D29" s="9">
-        <v>17500000</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>59</v>
@@ -6463,22 +6519,22 @@
     </row>
     <row r="30" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="11">
+        <v>7300000</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="D30" s="9">
-        <v>7300000</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>428</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>59</v>
@@ -6487,22 +6543,22 @@
     </row>
     <row r="31" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="11">
+        <v>11000000</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D31" s="9">
-        <v>11000000</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>59</v>
@@ -6511,22 +6567,22 @@
     </row>
     <row r="32" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="11">
+        <v>42000000</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="D32" s="9">
-        <v>42000000</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>434</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>59</v>
@@ -6535,22 +6591,22 @@
     </row>
     <row r="33" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="11">
+        <v>13600000</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D33" s="9">
-        <v>13600000</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>437</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>59</v>
@@ -6559,22 +6615,22 @@
     </row>
     <row r="34" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="11">
+        <v>12700000</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="D34" s="9">
-        <v>12700000</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>440</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>59</v>
@@ -6583,22 +6639,22 @@
     </row>
     <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="11">
+        <v>2000000</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D35" s="9">
-        <v>2000000</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>443</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>59</v>
@@ -6607,22 +6663,22 @@
     </row>
     <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>446</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>59</v>
@@ -6631,22 +6687,22 @@
     </row>
     <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="11">
+        <v>2300000</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D37" s="9">
-        <v>2300000</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>449</v>
-      </c>
       <c r="F37" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>59</v>
@@ -6655,22 +6711,22 @@
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="11">
+        <v>15000000</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="D38" s="9">
-        <v>15000000</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>452</v>
-      </c>
       <c r="F38" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>59</v>
@@ -6679,22 +6735,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>455</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>59</v>
@@ -6703,22 +6759,22 @@
     </row>
     <row r="40" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="11">
+        <v>100000000</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D40" s="9">
-        <v>100000000</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>458</v>
-      </c>
       <c r="F40" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>91</v>
@@ -6727,22 +6783,22 @@
     </row>
     <row r="41" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>461</v>
-      </c>
       <c r="F41" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>91</v>
@@ -6751,22 +6807,22 @@
     </row>
     <row r="42" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="D42" s="9">
+      <c r="D42" s="11">
         <v>175000000</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>88</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>91</v>
@@ -6775,22 +6831,22 @@
     </row>
     <row r="43" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="11">
+        <v>200000000</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D43" s="9">
-        <v>200000000</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="F43" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>91</v>
@@ -6799,22 +6855,22 @@
     </row>
     <row r="44" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="11">
+        <v>40000000</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="D44" s="9">
-        <v>40000000</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>469</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>91</v>
@@ -6823,22 +6879,22 @@
     </row>
     <row r="45" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="11">
+        <v>11700000</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="D45" s="9">
-        <v>11700000</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>472</v>
-      </c>
       <c r="F45" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>91</v>
@@ -6847,22 +6903,22 @@
     </row>
     <row r="46" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="11">
+        <v>65000000</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D46" s="9">
-        <v>65000000</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="F46" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>91</v>
@@ -6871,22 +6927,22 @@
     </row>
     <row r="47" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="11">
+        <v>53000000</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D47" s="9">
-        <v>53000000</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="F47" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>91</v>
@@ -6895,22 +6951,22 @@
     </row>
     <row r="48" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="11">
+        <v>120000000</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="D48" s="9">
-        <v>120000000</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>481</v>
-      </c>
       <c r="F48" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>91</v>
@@ -6919,22 +6975,22 @@
     </row>
     <row r="49" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="D49" s="11">
+        <v>5000000</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="D49" s="9">
-        <v>5000000</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>484</v>
-      </c>
       <c r="F49" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>91</v>
@@ -6943,22 +6999,22 @@
     </row>
     <row r="50" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="11">
+        <v>7000000</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="D50" s="9">
-        <v>7000000</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>487</v>
-      </c>
       <c r="F50" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>91</v>
@@ -6967,22 +7023,22 @@
     </row>
     <row r="51" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="11">
+        <v>17780000</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="D51" s="9">
-        <v>17780000</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="F51" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>91</v>
@@ -6991,22 +7047,22 @@
     </row>
     <row r="52" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="11">
+        <v>24000000</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D52" s="9">
-        <v>24000000</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="F52" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>91</v>
@@ -7015,22 +7071,22 @@
     </row>
     <row r="53" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" s="11">
+        <v>65000000</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="D53" s="9">
-        <v>65000000</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>496</v>
-      </c>
       <c r="F53" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>91</v>
@@ -7039,22 +7095,22 @@
     </row>
     <row r="54" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="11">
+        <v>175000000</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="D54" s="9">
-        <v>175000000</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="F54" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>91</v>
@@ -7063,22 +7119,22 @@
     </row>
     <row r="55" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C55" s="2" t="s">
+      <c r="D55" s="11">
+        <v>13000000</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="D55" s="9">
-        <v>13000000</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>502</v>
-      </c>
       <c r="F55" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>91</v>
@@ -7087,22 +7143,22 @@
     </row>
     <row r="56" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="11">
+        <v>10900000</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="D56" s="9">
-        <v>10900000</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>505</v>
-      </c>
       <c r="F56" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>91</v>
@@ -7111,22 +7167,22 @@
     </row>
     <row r="57" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C57" s="2" t="s">
+      <c r="D57" s="11">
+        <v>25000000</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="D57" s="9">
-        <v>25000000</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>508</v>
-      </c>
       <c r="F57" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>91</v>
@@ -7135,22 +7191,22 @@
     </row>
     <row r="58" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="D58" s="11">
+        <v>83000000</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="D58" s="9">
-        <v>83000000</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>511</v>
-      </c>
       <c r="F58" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>91</v>
@@ -7159,22 +7215,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="D59" s="9">
+      <c r="D59" s="11">
         <v>30000000</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>91</v>
@@ -7183,22 +7239,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="11">
+        <v>5200000</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D60" s="9">
-        <v>5200000</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>516</v>
-      </c>
       <c r="F60" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>91</v>
@@ -7207,22 +7263,22 @@
     </row>
     <row r="61" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="D61" s="11">
+        <v>100000000</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D61" s="9">
-        <v>100000000</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="F61" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>123</v>
@@ -7231,22 +7287,22 @@
     </row>
     <row r="62" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="11">
+        <v>1700000</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D62" s="9">
-        <v>1700000</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>522</v>
-      </c>
       <c r="F62" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>123</v>
@@ -7255,22 +7311,22 @@
     </row>
     <row r="63" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C63" s="2" t="s">
+      <c r="D63" s="11">
+        <v>200000000</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D63" s="9">
-        <v>200000000</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>525</v>
-      </c>
       <c r="F63" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>123</v>
@@ -7279,22 +7335,22 @@
     </row>
     <row r="64" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C64" s="2" t="s">
+      <c r="D64" s="11">
+        <v>38000000</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="D64" s="9">
-        <v>38000000</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>528</v>
-      </c>
       <c r="F64" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>123</v>
@@ -7303,22 +7359,22 @@
     </row>
     <row r="65" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C65" s="2" t="s">
+      <c r="D65" s="11">
+        <v>31000000</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D65" s="9">
-        <v>31000000</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>531</v>
-      </c>
       <c r="F65" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>123</v>
@@ -7327,22 +7383,22 @@
     </row>
     <row r="66" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C66" s="2" t="s">
+      <c r="D66" s="11">
+        <v>2000000</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="D66" s="9">
-        <v>2000000</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="F66" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>123</v>
@@ -7351,22 +7407,22 @@
     </row>
     <row r="67" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C67" s="2" t="s">
+      <c r="D67" s="11">
+        <v>3000000</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D67" s="9">
-        <v>3000000</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>537</v>
-      </c>
       <c r="F67" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>123</v>
@@ -7375,22 +7431,22 @@
     </row>
     <row r="68" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C68" s="2" t="s">
+      <c r="D68" s="11">
+        <v>7500000</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="D68" s="9">
-        <v>7500000</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>540</v>
-      </c>
       <c r="F68" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>123</v>
@@ -7399,22 +7455,22 @@
     </row>
     <row r="69" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C69" s="2" t="s">
+      <c r="D69" s="11">
+        <v>30000000</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="D69" s="9">
-        <v>30000000</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>543</v>
-      </c>
       <c r="F69" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>123</v>
@@ -7423,22 +7479,22 @@
     </row>
     <row r="70" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C70" s="2" t="s">
+      <c r="D70" s="11">
+        <v>11500000</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="D70" s="9">
-        <v>11500000</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>546</v>
-      </c>
       <c r="F70" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>123</v>
@@ -7447,22 +7503,22 @@
     </row>
     <row r="71" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C71" s="2" t="s">
+      <c r="D71" s="11">
+        <v>15000000</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="D71" s="9">
-        <v>15000000</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>549</v>
-      </c>
       <c r="F71" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>123</v>
@@ -7471,22 +7527,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C72" s="2" t="s">
+      <c r="D72" s="11">
+        <v>35000000</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="D72" s="9">
-        <v>35000000</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>552</v>
-      </c>
       <c r="F72" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>123</v>
@@ -7495,22 +7551,22 @@
     </row>
     <row r="73" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="11">
+        <v>9000000</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="D73" s="9">
-        <v>9000000</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>555</v>
-      </c>
       <c r="F73" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>123</v>
@@ -7519,22 +7575,22 @@
     </row>
     <row r="74" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C74" s="2" t="s">
+      <c r="D74" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="D74" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="F74" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>123</v>
@@ -7543,22 +7599,22 @@
     </row>
     <row r="75" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" s="11">
+        <v>35000000</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D75" s="9">
-        <v>35000000</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>561</v>
-      </c>
       <c r="F75" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>123</v>
@@ -7567,22 +7623,22 @@
     </row>
     <row r="76" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C76" s="2" t="s">
+      <c r="D76" s="11">
+        <v>10000000</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="D76" s="9">
-        <v>10000000</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>564</v>
-      </c>
       <c r="F76" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>123</v>
@@ -7591,22 +7647,22 @@
     </row>
     <row r="77" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C77" s="2" t="s">
+      <c r="D77" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="D77" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>567</v>
-      </c>
       <c r="F77" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>123</v>
@@ -7615,22 +7671,22 @@
     </row>
     <row r="78" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C78" s="2" t="s">
+      <c r="D78" s="11">
+        <v>14400000</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D78" s="9">
-        <v>14400000</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>570</v>
-      </c>
       <c r="F78" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>123</v>
@@ -7639,22 +7695,22 @@
     </row>
     <row r="79" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C79" s="2" t="s">
+      <c r="D79" s="11">
+        <v>6000000</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="D79" s="9">
-        <v>6000000</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>573</v>
-      </c>
       <c r="F79" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>123</v>
@@ -7663,22 +7719,22 @@
     </row>
     <row r="80" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C80" s="2" t="s">
+      <c r="D80" s="11">
+        <v>25000000</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="D80" s="9">
-        <v>25000000</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="F80" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>123</v>
@@ -7687,22 +7743,22 @@
     </row>
     <row r="81" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C81" s="2" t="s">
+      <c r="D81" s="11">
+        <v>2000000</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="D81" s="9">
-        <v>2000000</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>579</v>
-      </c>
       <c r="F81" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>123</v>
@@ -7711,22 +7767,22 @@
     </row>
     <row r="82" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C82" s="2" t="s">
+      <c r="D82" s="11">
+        <v>14300000</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="D82" s="9">
-        <v>14300000</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>582</v>
-      </c>
       <c r="F82" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>123</v>
@@ -7735,22 +7791,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C83" s="2" t="s">
+      <c r="D83" s="11">
+        <v>3175000</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="D83" s="9">
-        <v>3175000</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>585</v>
-      </c>
       <c r="F83" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>123</v>
@@ -7759,22 +7815,22 @@
     </row>
     <row r="84" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C84" s="2" t="s">
+      <c r="D84" s="11">
+        <v>1200000</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="D84" s="9">
-        <v>1200000</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>588</v>
-      </c>
       <c r="F84" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>123</v>
@@ -7783,22 +7839,22 @@
     </row>
     <row r="85" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C85" s="2" t="s">
+      <c r="D85" s="11">
+        <v>1270000</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="D85" s="9">
-        <v>1270000</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>591</v>
-      </c>
       <c r="F85" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>123</v>
@@ -7807,22 +7863,22 @@
     </row>
     <row r="86" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C86" s="2" t="s">
+      <c r="D86" s="11">
+        <v>20000000</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="D86" s="9">
-        <v>20000000</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="F86" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>123</v>
@@ -7831,22 +7887,22 @@
     </row>
     <row r="87" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C87" s="2" t="s">
+      <c r="D87" s="11">
+        <v>200000</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="D87" s="9">
-        <v>200000</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>597</v>
-      </c>
       <c r="F87" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>123</v>
@@ -7855,22 +7911,22 @@
     </row>
     <row r="88" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="D88" s="9">
+      <c r="D88" s="11">
         <v>13500000</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>163</v>
@@ -7879,22 +7935,22 @@
     </row>
     <row r="89" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C89" s="2" t="s">
+      <c r="D89" s="11">
+        <v>10000000</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="D89" s="9">
-        <v>10000000</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>602</v>
-      </c>
       <c r="F89" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>163</v>
@@ -7903,22 +7959,22 @@
     </row>
     <row r="90" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C90" s="2" t="s">
+      <c r="D90" s="11">
+        <v>42000000</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="D90" s="9">
-        <v>42000000</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>605</v>
-      </c>
       <c r="F90" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>163</v>
@@ -7927,22 +7983,22 @@
     </row>
     <row r="91" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C91" s="2" t="s">
+      <c r="D91" s="11">
+        <v>45000000</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="D91" s="9">
-        <v>45000000</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>608</v>
-      </c>
       <c r="F91" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>163</v>
@@ -7951,22 +8007,22 @@
     </row>
     <row r="92" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="D92" s="11">
+        <v>4500000</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="D92" s="9">
-        <v>4500000</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>611</v>
-      </c>
       <c r="F92" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>163</v>
@@ -7978,19 +8034,19 @@
         <v>244</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C93" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="D93" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>613</v>
-      </c>
       <c r="F93" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>163</v>
@@ -7999,22 +8055,22 @@
     </row>
     <row r="94" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C94" s="2" t="s">
+      <c r="D94" s="11">
+        <v>900000</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="D94" s="9">
-        <v>900000</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>616</v>
-      </c>
       <c r="F94" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>163</v>
@@ -8023,22 +8079,22 @@
     </row>
     <row r="95" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C95" s="2" t="s">
+      <c r="D95" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="D95" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>619</v>
-      </c>
       <c r="F95" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>163</v>
@@ -8047,22 +8103,22 @@
     </row>
     <row r="96" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="D96" s="11">
+        <v>36100000</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="D96" s="9">
-        <v>36100000</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>622</v>
-      </c>
       <c r="F96" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>163</v>
@@ -8071,22 +8127,22 @@
     </row>
     <row r="97" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="D97" s="11">
+        <v>4000000</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="D97" s="9">
-        <v>4000000</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>625</v>
-      </c>
       <c r="F97" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>163</v>
@@ -8095,22 +8151,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C98" s="2" t="s">
+      <c r="D98" s="11">
+        <v>2500000</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="D98" s="9">
-        <v>2500000</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>628</v>
-      </c>
       <c r="F98" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>163</v>
@@ -8119,22 +8175,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C99" s="2" t="s">
+      <c r="D99" s="11">
+        <v>2500000</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="D99" s="9">
-        <v>2500000</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>631</v>
-      </c>
       <c r="F99" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>163</v>
@@ -8143,22 +8199,22 @@
     </row>
     <row r="100" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C100" s="2" t="s">
+      <c r="D100" s="11">
+        <v>4500000</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="D100" s="9">
-        <v>4500000</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>634</v>
-      </c>
       <c r="F100" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>163</v>
@@ -8167,22 +8223,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="D101" s="9" t="s">
+      <c r="D101" s="11" t="s">
         <v>16</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>163</v>
@@ -8191,22 +8247,22 @@
     </row>
     <row r="102" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C102" s="2" t="s">
+      <c r="D102" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="D102" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>639</v>
-      </c>
       <c r="F102" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>163</v>
@@ -8215,22 +8271,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C103" s="2" t="s">
+      <c r="D103" s="11">
+        <v>1524000</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="D103" s="9">
-        <v>1524000</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>642</v>
-      </c>
       <c r="F103" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>163</v>
@@ -8239,22 +8295,22 @@
     </row>
     <row r="104" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C104" s="2" t="s">
+      <c r="D104" s="11">
+        <v>17900000</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="D104" s="9">
-        <v>17900000</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>645</v>
-      </c>
       <c r="F104" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>200</v>
@@ -8263,22 +8319,22 @@
     </row>
     <row r="105" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C105" s="2" t="s">
+      <c r="D105" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="D105" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>648</v>
-      </c>
       <c r="F105" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>200</v>
@@ -8287,22 +8343,22 @@
     </row>
     <row r="106" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C106" s="2" t="s">
+      <c r="D106" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="D106" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>651</v>
-      </c>
       <c r="F106" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>200</v>
@@ -8311,22 +8367,22 @@
     </row>
     <row r="107" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C107" s="2" t="s">
+      <c r="D107" s="11">
+        <v>6000000</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="D107" s="9">
-        <v>6000000</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>654</v>
-      </c>
       <c r="F107" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>200</v>
@@ -8335,22 +8391,22 @@
     </row>
     <row r="108" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C108" s="2" t="s">
+      <c r="D108" s="11">
+        <v>20000000</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="D108" s="9">
-        <v>20000000</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>657</v>
-      </c>
       <c r="F108" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>200</v>
@@ -8359,22 +8415,22 @@
     </row>
     <row r="109" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C109" s="2" t="s">
+      <c r="D109" s="11">
+        <v>16000000</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="D109" s="9">
-        <v>16000000</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>660</v>
-      </c>
       <c r="F109" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>200</v>
@@ -8383,22 +8439,22 @@
     </row>
     <row r="110" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C110" s="2" t="s">
+      <c r="D110" s="11">
+        <v>1180000</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="D110" s="9">
-        <v>1180000</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>663</v>
-      </c>
       <c r="F110" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>200</v>
@@ -8407,22 +8463,22 @@
     </row>
     <row r="111" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C111" s="2" t="s">
+      <c r="D111" s="11">
+        <v>6000000</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="D111" s="9">
-        <v>6000000</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>666</v>
-      </c>
       <c r="F111" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>200</v>
@@ -8431,22 +8487,22 @@
     </row>
     <row r="112" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C112" s="2" t="s">
+      <c r="D112" s="11">
+        <v>7909999</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="D112" s="9">
-        <v>7909999</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>669</v>
-      </c>
       <c r="F112" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>200</v>
@@ -8455,22 +8511,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="D113" s="9">
+      <c r="D113" s="11">
         <v>29400000</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>200</v>
@@ -8479,22 +8535,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C114" s="2" t="s">
+      <c r="D114" s="11">
+        <v>370000</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="D114" s="9">
-        <v>370000</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>674</v>
-      </c>
       <c r="F114" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>200</v>
@@ -8503,22 +8559,22 @@
     </row>
     <row r="115" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C115" s="2" t="s">
+      <c r="D115" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="D115" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>677</v>
-      </c>
       <c r="F115" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>200</v>
@@ -8527,22 +8583,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="D116" s="9">
+      <c r="D116" s="11">
         <v>7500000</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>200</v>
@@ -8551,22 +8607,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C117" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C117" s="2" t="s">
+      <c r="D117" s="11">
+        <v>1800000</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="D117" s="9">
-        <v>1800000</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>682</v>
-      </c>
       <c r="F117" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>200</v>
@@ -8575,22 +8631,22 @@
     </row>
     <row r="118" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C118" s="2" t="s">
+      <c r="D118" s="11">
+        <v>2300000</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D118" s="9">
-        <v>2300000</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>685</v>
-      </c>
       <c r="F118" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>200</v>
@@ -8599,19 +8655,19 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D119" s="9">
+      <c r="D119" s="11">
         <v>50000000</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>277</v>
@@ -8623,19 +8679,19 @@
     </row>
     <row r="120" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C120" s="2" t="s">
+      <c r="D120" s="11">
+        <v>2000000</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="D120" s="9">
-        <v>2000000</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>689</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>277</v>
@@ -8647,19 +8703,19 @@
     </row>
     <row r="121" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C121" s="2" t="s">
+      <c r="D121" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>692</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>277</v>
@@ -8671,19 +8727,19 @@
     </row>
     <row r="122" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C122" s="2" t="s">
+      <c r="D122" s="11">
+        <v>450000000</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="D122" s="9">
-        <v>450000000</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>695</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>277</v>
@@ -8695,19 +8751,19 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C123" s="2" t="s">
+      <c r="D123" s="11">
+        <v>27300000</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="D123" s="9">
-        <v>27300000</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>277</v>
@@ -8719,19 +8775,19 @@
     </row>
     <row r="124" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C124" s="2" t="s">
+      <c r="D124" s="11">
+        <v>11500000</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>700</v>
-      </c>
-      <c r="D124" s="9">
-        <v>11500000</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>701</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>277</v>
@@ -8743,19 +8799,19 @@
     </row>
     <row r="125" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C125" s="2" t="s">
+      <c r="D125" s="11">
+        <v>30000000</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>703</v>
-      </c>
-      <c r="D125" s="9">
-        <v>30000000</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>704</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>277</v>
@@ -8767,19 +8823,19 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="D126" s="9">
+      <c r="D126" s="11">
         <v>20000000</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>277</v>
@@ -8791,19 +8847,19 @@
     </row>
     <row r="127" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C127" s="2" t="s">
+      <c r="D127" s="11">
+        <v>10000000</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="D127" s="9">
-        <v>10000000</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>708</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>277</v>
@@ -8815,19 +8871,19 @@
     </row>
     <row r="128" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C128" s="2" t="s">
+      <c r="D128" s="11">
+        <v>56000000</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="D128" s="9">
-        <v>56000000</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>711</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>277</v>
@@ -8839,19 +8895,19 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C129" s="2" t="s">
+      <c r="D129" s="11">
+        <v>12000000</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="D129" s="9">
-        <v>12000000</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>714</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>277</v>
@@ -8863,19 +8919,19 @@
     </row>
     <row r="130" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C130" s="2" t="s">
+      <c r="D130" s="11">
+        <v>20000000</v>
+      </c>
+      <c r="E130" s="2" t="s">
         <v>716</v>
-      </c>
-      <c r="D130" s="9">
-        <v>20000000</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>717</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>277</v>
@@ -8887,19 +8943,19 @@
     </row>
     <row r="131" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C131" s="2" t="s">
+      <c r="D131" s="11">
+        <v>27500000</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>719</v>
-      </c>
-      <c r="D131" s="9">
-        <v>27500000</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>720</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>277</v>
@@ -8911,19 +8967,19 @@
     </row>
     <row r="132" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C132" s="2" t="s">
+      <c r="D132" s="11">
+        <v>4700000</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="D132" s="9">
-        <v>4700000</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>723</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>277</v>
@@ -8935,15 +8991,15 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="D133" s="9">
+      <c r="D133" s="11">
         <v>14000000</v>
       </c>
       <c r="E133" s="2" t="s">
@@ -8959,19 +9015,19 @@
     </row>
     <row r="134" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C134" s="2" t="s">
+      <c r="D134" s="11">
+        <v>250000</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="D134" s="9">
-        <v>250000</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>277</v>
@@ -8983,19 +9039,19 @@
     </row>
     <row r="135" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C135" s="2" t="s">
+      <c r="D135" s="11">
+        <v>1200000</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>730</v>
-      </c>
-      <c r="D135" s="9">
-        <v>1200000</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>731</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>277</v>
@@ -9007,19 +9063,19 @@
     </row>
     <row r="136" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C136" s="2" t="s">
+      <c r="D136" s="11">
+        <v>11000000</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="D136" s="9">
-        <v>11000000</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>734</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>277</v>
@@ -9031,19 +9087,19 @@
     </row>
     <row r="137" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C137" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C137" s="2" t="s">
+      <c r="D137" s="11">
+        <v>40000000</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="D137" s="9">
-        <v>40000000</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>737</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>277</v>
@@ -9055,19 +9111,19 @@
     </row>
     <row r="138" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C138" s="2" t="s">
+      <c r="D138" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E138" s="2" t="s">
         <v>739</v>
-      </c>
-      <c r="D138" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>740</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>277</v>
@@ -9079,19 +9135,19 @@
     </row>
     <row r="139" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C139" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C139" s="2" t="s">
+      <c r="D139" s="11">
+        <v>16000000</v>
+      </c>
+      <c r="E139" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="D139" s="9">
-        <v>16000000</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>743</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>277</v>
@@ -9103,19 +9159,19 @@
     </row>
     <row r="140" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C140" s="2" t="s">
+      <c r="D140" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>745</v>
-      </c>
-      <c r="D140" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>746</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>277</v>
@@ -9127,19 +9183,19 @@
     </row>
     <row r="141" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C141" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C141" s="2" t="s">
+      <c r="D141" s="11">
+        <v>2500000</v>
+      </c>
+      <c r="E141" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="D141" s="9">
-        <v>2500000</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>277</v>
@@ -9151,19 +9207,19 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="D142" s="11">
+        <v>12000000</v>
+      </c>
+      <c r="E142" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="D142" s="9">
-        <v>12000000</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>751</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>277</v>
@@ -9175,19 +9231,19 @@
     </row>
     <row r="143" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C143" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C143" s="2" t="s">
+      <c r="D143" s="11">
+        <v>1440000</v>
+      </c>
+      <c r="E143" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="D143" s="9">
-        <v>1440000</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>277</v>
@@ -9199,19 +9255,19 @@
     </row>
     <row r="144" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C144" s="2" t="s">
+      <c r="D144" s="11">
+        <v>2857500</v>
+      </c>
+      <c r="E144" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="D144" s="9">
-        <v>2857500</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>277</v>
@@ -9223,19 +9279,19 @@
     </row>
     <row r="145" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C145" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C145" s="2" t="s">
+      <c r="D145" s="11">
+        <v>2300000</v>
+      </c>
+      <c r="E145" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="D145" s="9">
-        <v>2300000</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>760</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>277</v>
@@ -9247,19 +9303,19 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C146" s="2" t="s">
+      <c r="D146" s="11">
+        <v>35000000</v>
+      </c>
+      <c r="E146" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="D146" s="9">
-        <v>35000000</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>763</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>277</v>
@@ -9271,231 +9327,231 @@
     </row>
     <row r="147" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C147" s="2" t="s">
+      <c r="D147" s="11">
+        <v>50000000</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="D147" s="9">
-        <v>50000000</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>766</v>
-      </c>
       <c r="F147" s="2" t="s">
         <v>277</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H147" s="2"/>
     </row>
     <row r="148" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C148" s="2" t="s">
+      <c r="D148" s="11">
+        <v>8200000</v>
+      </c>
+      <c r="E148" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="D148" s="9">
-        <v>8200000</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>769</v>
-      </c>
       <c r="F148" s="2" t="s">
         <v>277</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H148" s="2"/>
     </row>
     <row r="149" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="B149" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C149" s="2" t="s">
+      <c r="D149" s="11">
+        <v>4500000</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="D149" s="9">
-        <v>4500000</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>772</v>
-      </c>
       <c r="F149" s="2" t="s">
         <v>277</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H149" s="2"/>
     </row>
     <row r="150" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C150" s="2" t="s">
+      <c r="D150" s="11">
+        <v>75000000</v>
+      </c>
+      <c r="E150" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="D150" s="9">
-        <v>75000000</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>775</v>
-      </c>
       <c r="F150" s="2" t="s">
         <v>277</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H150" s="2"/>
     </row>
     <row r="151" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C151" s="2" t="s">
+      <c r="D151" s="11">
+        <v>24000000</v>
+      </c>
+      <c r="E151" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="D151" s="9">
-        <v>24000000</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>778</v>
-      </c>
       <c r="F151" s="2" t="s">
         <v>277</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H151" s="2"/>
     </row>
     <row r="152" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C152" s="2" t="s">
+      <c r="D152" s="11">
+        <v>16000000</v>
+      </c>
+      <c r="E152" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="D152" s="9">
-        <v>16000000</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>781</v>
-      </c>
       <c r="F152" s="2" t="s">
         <v>277</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H152" s="2"/>
     </row>
     <row r="153" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C153" s="2" t="s">
+      <c r="D153" s="11">
+        <v>8000000</v>
+      </c>
+      <c r="E153" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="D153" s="9">
-        <v>8000000</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>784</v>
-      </c>
       <c r="F153" s="2" t="s">
         <v>277</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H153" s="2"/>
     </row>
     <row r="154" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C154" s="2" t="s">
+      <c r="D154" s="11">
+        <v>1304000</v>
+      </c>
+      <c r="E154" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="D154" s="9">
-        <v>1304000</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>787</v>
-      </c>
       <c r="F154" s="2" t="s">
         <v>277</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H154" s="2"/>
     </row>
     <row r="155" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C155" s="2" t="s">
+      <c r="D155" s="11">
+        <v>400000</v>
+      </c>
+      <c r="E155" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="D155" s="9">
-        <v>400000</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>790</v>
-      </c>
       <c r="F155" s="2" t="s">
         <v>277</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H155" s="2"/>
     </row>
     <row r="156" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="D156" s="9">
+      <c r="D156" s="11">
         <v>7000000</v>
       </c>
       <c r="E156" s="2" t="s">
@@ -9511,19 +9567,19 @@
     </row>
     <row r="157" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C157" s="2" t="s">
+      <c r="D157" s="11">
+        <v>67000000</v>
+      </c>
+      <c r="E157" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="D157" s="9">
-        <v>67000000</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>795</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>277</v>
@@ -9535,19 +9591,19 @@
     </row>
     <row r="158" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C158" s="2" t="s">
+      <c r="D158" s="11">
+        <v>10000000</v>
+      </c>
+      <c r="E158" s="2" t="s">
         <v>797</v>
-      </c>
-      <c r="D158" s="9">
-        <v>10000000</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>798</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>277</v>
@@ -9559,19 +9615,19 @@
     </row>
     <row r="159" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C159" s="2" t="s">
+      <c r="D159" s="11">
+        <v>120000000</v>
+      </c>
+      <c r="E159" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="D159" s="9">
-        <v>120000000</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>801</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>277</v>
@@ -9583,19 +9639,19 @@
     </row>
     <row r="160" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C160" s="2" t="s">
+      <c r="D160" s="11">
+        <v>85000000</v>
+      </c>
+      <c r="E160" s="2" t="s">
         <v>803</v>
-      </c>
-      <c r="D160" s="9">
-        <v>85000000</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>804</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>277</v>
@@ -9607,19 +9663,19 @@
     </row>
     <row r="161" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C161" s="2" t="s">
+      <c r="D161" s="11">
+        <v>162500000</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="D161" s="9">
-        <v>162500000</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>807</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>277</v>
@@ -9631,19 +9687,19 @@
     </row>
     <row r="162" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C162" s="2" t="s">
+      <c r="D162" s="11">
+        <v>60000000</v>
+      </c>
+      <c r="E162" s="2" t="s">
         <v>809</v>
-      </c>
-      <c r="D162" s="9">
-        <v>60000000</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>810</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>277</v>
@@ -9655,19 +9711,19 @@
     </row>
     <row r="163" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C163" s="2" t="s">
+      <c r="D163" s="11">
+        <v>238000000</v>
+      </c>
+      <c r="E163" s="2" t="s">
         <v>812</v>
-      </c>
-      <c r="D163" s="9">
-        <v>238000000</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>813</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>277</v>
@@ -9679,19 +9735,19 @@
     </row>
     <row r="164" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C164" s="2" t="s">
+      <c r="D164" s="11">
+        <v>8000000</v>
+      </c>
+      <c r="E164" s="2" t="s">
         <v>815</v>
-      </c>
-      <c r="D164" s="9">
-        <v>8000000</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>816</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>277</v>
@@ -9703,19 +9759,19 @@
     </row>
     <row r="165" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C165" s="2" t="s">
+      <c r="D165" s="11">
+        <v>316700000</v>
+      </c>
+      <c r="E165" s="2" t="s">
         <v>818</v>
-      </c>
-      <c r="D165" s="9">
-        <v>316700000</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>819</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>277</v>
@@ -9727,19 +9783,19 @@
     </row>
     <row r="166" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C166" s="2" t="s">
+      <c r="D166" s="11">
+        <v>170000000</v>
+      </c>
+      <c r="E166" s="2" t="s">
         <v>821</v>
-      </c>
-      <c r="D166" s="9">
-        <v>170000000</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>822</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>277</v>
@@ -9751,19 +9807,19 @@
     </row>
     <row r="167" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C167" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C167" s="2" t="s">
+      <c r="D167" s="11">
+        <v>130000000</v>
+      </c>
+      <c r="E167" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="D167" s="9">
-        <v>130000000</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>825</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>277</v>
@@ -9775,19 +9831,19 @@
     </row>
     <row r="168" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C168" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="B168" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C168" s="2" t="s">
+      <c r="D168" s="11">
+        <v>110000000</v>
+      </c>
+      <c r="E168" s="2" t="s">
         <v>827</v>
-      </c>
-      <c r="D168" s="9">
-        <v>110000000</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>828</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>277</v>
@@ -9799,19 +9855,19 @@
     </row>
     <row r="169" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C169" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C169" s="2" t="s">
+      <c r="D169" s="11">
+        <v>65000000</v>
+      </c>
+      <c r="E169" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="D169" s="9">
-        <v>65000000</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>831</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>277</v>
@@ -9823,19 +9879,19 @@
     </row>
     <row r="170" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="B170" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C170" s="2" t="s">
+      <c r="D170" s="11">
+        <v>104000000</v>
+      </c>
+      <c r="E170" s="2" t="s">
         <v>833</v>
-      </c>
-      <c r="D170" s="9">
-        <v>104000000</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>834</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>277</v>
@@ -9847,19 +9903,19 @@
     </row>
     <row r="171" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C171" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="B171" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C171" s="2" t="s">
+      <c r="D171" s="11">
+        <v>16000000</v>
+      </c>
+      <c r="E171" s="2" t="s">
         <v>836</v>
-      </c>
-      <c r="D171" s="9">
-        <v>16000000</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>837</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>277</v>
@@ -9871,19 +9927,19 @@
     </row>
     <row r="172" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="B172" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C172" s="2" t="s">
+      <c r="D172" s="11">
+        <v>1270000</v>
+      </c>
+      <c r="E172" s="2" t="s">
         <v>839</v>
-      </c>
-      <c r="D172" s="9">
-        <v>1270000</v>
-      </c>
-      <c r="E172" s="2" t="s">
-        <v>840</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>277</v>
@@ -9898,16 +9954,16 @@
         <v>208</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D173" s="9">
+      <c r="D173" s="11">
         <v>50000000</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>277</v>
@@ -9919,19 +9975,19 @@
     </row>
     <row r="174" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="B174" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C174" s="2" t="s">
+      <c r="D174" s="11">
+        <v>323850</v>
+      </c>
+      <c r="E174" s="2" t="s">
         <v>842</v>
-      </c>
-      <c r="D174" s="9">
-        <v>323850</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>843</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>277</v>
@@ -9943,19 +9999,19 @@
     </row>
     <row r="175" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C175" s="2" t="s">
+      <c r="D175" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E175" s="2" t="s">
         <v>845</v>
-      </c>
-      <c r="D175" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>846</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>277</v>
@@ -9967,19 +10023,19 @@
     </row>
     <row r="176" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C176" s="2" t="s">
         <v>847</v>
       </c>
-      <c r="B176" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C176" s="2" t="s">
+      <c r="D176" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E176" s="2" t="s">
         <v>848</v>
-      </c>
-      <c r="D176" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>849</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>277</v>
@@ -9991,19 +10047,19 @@
     </row>
     <row r="177" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C177" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C177" s="2" t="s">
+      <c r="D177" s="11">
+        <v>2800000</v>
+      </c>
+      <c r="E177" s="2" t="s">
         <v>851</v>
-      </c>
-      <c r="D177" s="9">
-        <v>2800000</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>852</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>277</v>
@@ -10015,19 +10071,19 @@
     </row>
     <row r="178" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>853</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C178" s="2" t="s">
+      <c r="D178" s="11">
+        <v>85000000</v>
+      </c>
+      <c r="E178" s="2" t="s">
         <v>854</v>
-      </c>
-      <c r="D178" s="9">
-        <v>85000000</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>855</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>277</v>
@@ -10039,19 +10095,19 @@
     </row>
     <row r="179" spans="1:8" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C179" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C179" s="2" t="s">
+      <c r="D179" s="11">
+        <v>100000000</v>
+      </c>
+      <c r="E179" s="2" t="s">
         <v>857</v>
-      </c>
-      <c r="D179" s="9">
-        <v>100000000</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>858</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>277</v>
@@ -10063,15 +10119,15 @@
     </row>
     <row r="180" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>859</v>
       </c>
-      <c r="B180" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="D180" s="9">
+      <c r="D180" s="11">
         <v>4875000</v>
       </c>
       <c r="E180" s="2" t="s">
@@ -10087,15 +10143,15 @@
     </row>
     <row r="181" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="D181" s="9">
+        <v>860</v>
+      </c>
+      <c r="D181" s="11">
         <v>5000000</v>
       </c>
       <c r="E181" s="2" t="s">
@@ -10111,19 +10167,19 @@
     </row>
     <row r="182" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C182" s="2" t="s">
+      <c r="D182" s="11">
+        <v>90000000</v>
+      </c>
+      <c r="E182" s="2" t="s">
         <v>863</v>
-      </c>
-      <c r="D182" s="9">
-        <v>90000000</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>864</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>277</v>
@@ -10135,19 +10191,19 @@
     </row>
     <row r="183" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C183" s="2" t="s">
+      <c r="D183" s="11">
+        <v>10000000</v>
+      </c>
+      <c r="E183" s="2" t="s">
         <v>866</v>
-      </c>
-      <c r="D183" s="9">
-        <v>10000000</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>867</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>277</v>
@@ -10159,15 +10215,15 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="B184" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="D184" s="10">
+      <c r="D184" s="12">
         <v>4500000</v>
       </c>
       <c r="E184" s="2" t="s">
@@ -10180,76 +10236,76 @@
         <v>231</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="D185" s="10">
+        <v>895</v>
+      </c>
+      <c r="D185" s="12">
         <v>7500000</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>200</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C186" s="2" t="s">
         <v>897</v>
       </c>
-      <c r="B186" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C186" s="2" t="s">
+      <c r="D186" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="E186" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="D186" s="10">
-        <v>2000000</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>899</v>
-      </c>
       <c r="F186" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C187" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="D187" s="12">
+        <v>11600000</v>
+      </c>
+      <c r="E187" s="2" t="s">
         <v>900</v>
-      </c>
-      <c r="D187" s="10">
-        <v>11600000</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>901</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>277</v>
@@ -10258,62 +10314,63 @@
         <v>231</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="D188" s="10">
+        <v>901</v>
+      </c>
+      <c r="D188" s="12">
         <v>29400000</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>200</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C189" s="2" t="s">
         <v>903</v>
       </c>
-      <c r="B189" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="D189" s="10">
+      <c r="D189" s="12">
         <v>3000000</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>163</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H189" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10336,36 +10393,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>883</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>884</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>874</v>
+      </c>
+      <c r="B2" t="s">
         <v>875</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>876</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>877</v>
-      </c>
-      <c r="D2" t="s">
-        <v>878</v>
       </c>
       <c r="E2" s="3">
         <v>17000000</v>
@@ -10373,22 +10430,22 @@
       <c r="F2" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>45898</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C3" t="s">
+        <v>878</v>
+      </c>
+      <c r="D3" t="s">
         <v>879</v>
-      </c>
-      <c r="D3" t="s">
-        <v>880</v>
       </c>
       <c r="E3" s="3">
         <v>75000000</v>
@@ -10396,145 +10453,145 @@
       <c r="F3" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>45868</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>905</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>876</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>906</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="7" t="s">
+        <v>917</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="G4" s="6">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>907</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="B5" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F5" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="G5" s="6">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>872</v>
       </c>
-      <c r="G4" s="7">
-        <v>45658</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>908</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>876</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>909</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>907</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>919</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="G5" s="7">
-        <v>45717</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>910</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>876</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="G6" s="6">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>911</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>907</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D7" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>920</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>873</v>
-      </c>
-      <c r="G6" s="7">
-        <v>45809</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>718</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>876</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="F7" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="G7" s="6">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>907</v>
-      </c>
-      <c r="E7" s="8" t="s">
+      <c r="B8" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>921</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G7" s="7">
-        <v>45839</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>913</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>876</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="F8" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="G8" s="6">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>914</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>907</v>
-      </c>
-      <c r="E8" s="8" t="s">
+      <c r="D9" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>922</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G8" s="7">
-        <v>45870</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>876</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>915</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>916</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>923</v>
-      </c>
       <c r="F9" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>45901</v>
       </c>
     </row>

--- a/data/MedTech_YTD_Standardized.xlsx
+++ b/data/MedTech_YTD_Standardized.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beacononehcp-my.sharepoint.com/personal/hannah_peric_beacononehcp_com/Documents/Documents/medtech-dashboard/Medtech-Dashboard-M-A/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8437E4D-B5B8-4C39-A7F4-F05CB8740D97}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66DCCE4D-8DDF-4FCF-A07A-749B2DCFB4DB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD M&amp;A Activity" sheetId="1" r:id="rId1"/>
@@ -2807,8 +2807,8 @@
   <numFmts count="4">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -2898,11 +2898,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3219,7 +3219,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3281,7 +3280,7 @@
       </c>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
@@ -3329,7 +3328,7 @@
       </c>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
@@ -3353,7 +3352,7 @@
       </c>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
@@ -3377,7 +3376,7 @@
       </c>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>27</v>
       </c>
@@ -3401,7 +3400,7 @@
       </c>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>30</v>
       </c>
@@ -3425,7 +3424,7 @@
       </c>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
@@ -3449,7 +3448,7 @@
       </c>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>36</v>
       </c>
@@ -3473,7 +3472,7 @@
       </c>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>39</v>
       </c>
@@ -3497,7 +3496,7 @@
       </c>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>42</v>
       </c>
@@ -3521,7 +3520,7 @@
       </c>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>45</v>
       </c>
@@ -3545,7 +3544,7 @@
       </c>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>48</v>
       </c>
@@ -3569,7 +3568,7 @@
       </c>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>51</v>
       </c>
@@ -3593,7 +3592,7 @@
       </c>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>54</v>
       </c>
@@ -3617,7 +3616,7 @@
       </c>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>57</v>
       </c>
@@ -3641,7 +3640,7 @@
       </c>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>60</v>
       </c>
@@ -3665,7 +3664,7 @@
       </c>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>63</v>
       </c>
@@ -3689,7 +3688,7 @@
       </c>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>66</v>
       </c>
@@ -3737,7 +3736,7 @@
       </c>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>73</v>
       </c>
@@ -3809,7 +3808,7 @@
       </c>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>84</v>
       </c>
@@ -3857,7 +3856,7 @@
       </c>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>92</v>
       </c>
@@ -3905,7 +3904,7 @@
       </c>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>99</v>
       </c>
@@ -3929,7 +3928,7 @@
       </c>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>102</v>
       </c>
@@ -3953,7 +3952,7 @@
       </c>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>105</v>
       </c>
@@ -4001,7 +4000,7 @@
       </c>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>112</v>
       </c>
@@ -4049,7 +4048,7 @@
       </c>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>120</v>
       </c>
@@ -4145,7 +4144,7 @@
       </c>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>135</v>
       </c>
@@ -4169,7 +4168,7 @@
       </c>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -4193,7 +4192,7 @@
       </c>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>142</v>
       </c>
@@ -4289,7 +4288,7 @@
       </c>
       <c r="H44" s="4"/>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>157</v>
       </c>
@@ -4313,7 +4312,7 @@
       </c>
       <c r="H45" s="4"/>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>160</v>
       </c>
@@ -4385,7 +4384,7 @@
       </c>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>172</v>
       </c>
@@ -4409,7 +4408,7 @@
       </c>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>175</v>
       </c>
@@ -4433,7 +4432,7 @@
       </c>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>177</v>
       </c>
@@ -4481,7 +4480,7 @@
       </c>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>184</v>
       </c>
@@ -4529,7 +4528,7 @@
       </c>
       <c r="H54" s="4"/>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>191</v>
       </c>
@@ -4553,7 +4552,7 @@
       </c>
       <c r="H55" s="4"/>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>194</v>
       </c>
@@ -4577,7 +4576,7 @@
       </c>
       <c r="H56" s="4"/>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>197</v>
       </c>
@@ -4601,7 +4600,7 @@
       </c>
       <c r="H57" s="4"/>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>201</v>
       </c>
@@ -4673,7 +4672,7 @@
       </c>
       <c r="H60" s="4"/>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>212</v>
       </c>
@@ -4867,7 +4866,7 @@
       </c>
       <c r="H68" s="4"/>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>241</v>
       </c>
@@ -4891,7 +4890,7 @@
       </c>
       <c r="H69" s="4"/>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>244</v>
       </c>
@@ -4915,7 +4914,7 @@
       </c>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>247</v>
       </c>
@@ -4939,7 +4938,7 @@
       </c>
       <c r="H71" s="4"/>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>248</v>
       </c>
@@ -4963,7 +4962,7 @@
       </c>
       <c r="H72" s="4"/>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>251</v>
       </c>
@@ -4987,7 +4986,7 @@
       </c>
       <c r="H73" s="4"/>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>254</v>
       </c>
@@ -5011,7 +5010,7 @@
       </c>
       <c r="H74" s="4"/>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>257</v>
       </c>
@@ -5035,7 +5034,7 @@
       </c>
       <c r="H75" s="4"/>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>873</v>
       </c>
@@ -5083,7 +5082,7 @@
       </c>
       <c r="H77" s="4"/>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>265</v>
       </c>
@@ -5107,7 +5106,7 @@
       </c>
       <c r="H78" s="4"/>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>268</v>
       </c>
@@ -5131,7 +5130,7 @@
       </c>
       <c r="H79" s="4"/>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>271</v>
       </c>
@@ -5155,7 +5154,7 @@
       </c>
       <c r="H80" s="4"/>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>274</v>
       </c>
@@ -5179,7 +5178,7 @@
       </c>
       <c r="H81" s="4"/>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>278</v>
       </c>
@@ -5203,7 +5202,7 @@
       </c>
       <c r="H82" s="4"/>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>280</v>
       </c>
@@ -5227,7 +5226,7 @@
       </c>
       <c r="H83" s="4"/>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>283</v>
       </c>
@@ -5251,7 +5250,7 @@
       </c>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>286</v>
       </c>
@@ -5275,7 +5274,7 @@
       </c>
       <c r="H85" s="4"/>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>289</v>
       </c>
@@ -5299,7 +5298,7 @@
       </c>
       <c r="H86" s="4"/>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>292</v>
       </c>
@@ -5347,7 +5346,7 @@
       </c>
       <c r="H88" s="4"/>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>297</v>
       </c>
@@ -5371,7 +5370,7 @@
       </c>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>300</v>
       </c>
@@ -5395,7 +5394,7 @@
       </c>
       <c r="H90" s="4"/>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>302</v>
       </c>
@@ -5419,7 +5418,7 @@
       </c>
       <c r="H91" s="4"/>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>307</v>
       </c>
@@ -5443,7 +5442,7 @@
       </c>
       <c r="H92" s="4"/>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>310</v>
       </c>
@@ -5467,7 +5466,7 @@
       </c>
       <c r="H93" s="4"/>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>312</v>
       </c>
@@ -5491,7 +5490,7 @@
       </c>
       <c r="H94" s="4"/>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>315</v>
       </c>
@@ -5515,7 +5514,7 @@
       </c>
       <c r="H95" s="4"/>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>318</v>
       </c>
@@ -5539,7 +5538,7 @@
       </c>
       <c r="H96" s="4"/>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>321</v>
       </c>
@@ -5563,7 +5562,7 @@
       </c>
       <c r="H97" s="4"/>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>323</v>
       </c>
@@ -5587,7 +5586,7 @@
       </c>
       <c r="H98" s="4"/>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>325</v>
       </c>
@@ -5683,7 +5682,7 @@
       </c>
       <c r="H102" s="4"/>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>337</v>
       </c>
@@ -5733,7 +5732,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>888</v>
       </c>
@@ -5760,45 +5759,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H105" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="$1,100,000,000"/>
-        <filter val="$1,500,000,000"/>
-        <filter val="$100,000,000"/>
-        <filter val="$120,000,000"/>
-        <filter val="$130,000,000"/>
-        <filter val="$15000000"/>
-        <filter val="$152,000,000"/>
-        <filter val="$17,000,000"/>
-        <filter val="$17,500,000,000"/>
-        <filter val="$18300000000"/>
-        <filter val="$225,000,000"/>
-        <filter val="$2250000000"/>
-        <filter val="$250,000,000"/>
-        <filter val="$256,000,000"/>
-        <filter val="$30000000"/>
-        <filter val="$350,000,000"/>
-        <filter val="$4,100,000,000"/>
-        <filter val="$4,900,000,000"/>
-        <filter val="$425,000,000"/>
-        <filter val="$430,000,000"/>
-        <filter val="$497,000,000"/>
-        <filter val="$5,100,000,000"/>
-        <filter val="$517,000,000"/>
-        <filter val="$533,000,000"/>
-        <filter val="$540,000,000"/>
-        <filter val="$6,000,000"/>
-        <filter val="$664,000,000"/>
-        <filter val="$815000000"/>
-        <filter val="$85,000,000"/>
-        <filter val="$88 million"/>
-        <filter val="$88,000,000"/>
-        <filter val="$883,000,000"/>
-        <filter val="$9,000,000"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H105" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/data/MedTech_YTD_Standardized.xlsx
+++ b/data/MedTech_YTD_Standardized.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beacononehcp-my.sharepoint.com/personal/hannah_peric_beacononehcp_com/Documents/Documents/medtech-dashboard/Medtech-Dashboard-M-A/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66DCCE4D-8DDF-4FCF-A07A-749B2DCFB4DB}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="8_{65FA6BF7-B91C-4C17-A0B0-D806B42CDDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE7DF1A2-9F99-434B-9697-47D906E67554}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD M&amp;A Activity" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="922">
   <si>
     <t>Company</t>
   </si>
@@ -2627,12 +2627,6 @@
   </si>
   <si>
     <t>K50 Ventures (led), TSVC (led), Draper, ShangBay Capital, Eliot Horowitz, Dr. Fred Moll</t>
-  </si>
-  <si>
-    <t>$18300000000</t>
-  </si>
-  <si>
-    <t>$815000000</t>
   </si>
   <si>
     <t>$30000000</t>
@@ -2875,7 +2869,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2905,6 +2899,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -3253,7 +3248,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3273,7 +3268,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>12</v>
@@ -3297,7 +3292,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>12</v>
@@ -3321,7 +3316,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>12</v>
@@ -3345,7 +3340,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>12</v>
@@ -3369,7 +3364,7 @@
         <v>16</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>12</v>
@@ -3393,7 +3388,7 @@
         <v>16</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>12</v>
@@ -3417,7 +3412,7 @@
         <v>16</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>12</v>
@@ -3441,7 +3436,7 @@
         <v>16</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>12</v>
@@ -3465,7 +3460,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>12</v>
@@ -3489,7 +3484,7 @@
         <v>16</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>12</v>
@@ -3513,7 +3508,7 @@
         <v>16</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>12</v>
@@ -3537,7 +3532,7 @@
         <v>16</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>12</v>
@@ -3561,7 +3556,7 @@
         <v>16</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>12</v>
@@ -3585,7 +3580,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>12</v>
@@ -3609,7 +3604,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>12</v>
@@ -3633,7 +3628,7 @@
         <v>16</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>59</v>
@@ -3657,7 +3652,7 @@
         <v>16</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>59</v>
@@ -3681,7 +3676,7 @@
         <v>16</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>59</v>
@@ -3705,7 +3700,7 @@
         <v>16</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>59</v>
@@ -3729,7 +3724,7 @@
         <v>72</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>59</v>
@@ -3753,7 +3748,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>59</v>
@@ -3777,7 +3772,7 @@
         <v>79</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>59</v>
@@ -3801,7 +3796,7 @@
         <v>83</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>59</v>
@@ -3825,7 +3820,7 @@
         <v>16</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>59</v>
@@ -3849,7 +3844,7 @@
         <v>90</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>91</v>
@@ -3873,7 +3868,7 @@
         <v>16</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>91</v>
@@ -3897,7 +3892,7 @@
         <v>98</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>91</v>
@@ -3921,7 +3916,7 @@
         <v>16</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>91</v>
@@ -3945,7 +3940,7 @@
         <v>16</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>91</v>
@@ -3969,7 +3964,7 @@
         <v>16</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>91</v>
@@ -3993,7 +3988,7 @@
         <v>111</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>91</v>
@@ -4017,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>91</v>
@@ -4041,7 +4036,7 @@
         <v>119</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>91</v>
@@ -4065,7 +4060,7 @@
         <v>16</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>123</v>
@@ -4089,7 +4084,7 @@
         <v>127</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>123</v>
@@ -4113,7 +4108,7 @@
         <v>130</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>123</v>
@@ -4137,7 +4132,7 @@
         <v>134</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>123</v>
@@ -4161,7 +4156,7 @@
         <v>16</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>123</v>
@@ -4185,7 +4180,7 @@
         <v>16</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>123</v>
@@ -4209,7 +4204,7 @@
         <v>16</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>123</v>
@@ -4233,7 +4228,7 @@
         <v>148</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>123</v>
@@ -4257,7 +4252,7 @@
         <v>152</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>123</v>
@@ -4281,7 +4276,7 @@
         <v>156</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>123</v>
@@ -4305,7 +4300,7 @@
         <v>16</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>123</v>
@@ -4329,7 +4324,7 @@
         <v>16</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>163</v>
@@ -4353,7 +4348,7 @@
         <v>167</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>163</v>
@@ -4377,7 +4372,7 @@
         <v>171</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>163</v>
@@ -4401,7 +4396,7 @@
         <v>16</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>163</v>
@@ -4425,7 +4420,7 @@
         <v>16</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>163</v>
@@ -4449,7 +4444,7 @@
         <v>16</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>163</v>
@@ -4473,7 +4468,7 @@
         <v>183</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>163</v>
@@ -4497,7 +4492,7 @@
         <v>16</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>163</v>
@@ -4521,7 +4516,7 @@
         <v>190</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>163</v>
@@ -4545,7 +4540,7 @@
         <v>16</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>163</v>
@@ -4569,7 +4564,7 @@
         <v>16</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>163</v>
@@ -4593,7 +4588,7 @@
         <v>16</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>200</v>
@@ -4617,7 +4612,7 @@
         <v>16</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>200</v>
@@ -4641,7 +4636,7 @@
         <v>207</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>200</v>
@@ -4767,7 +4762,7 @@
         <v>215</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4931,7 +4926,7 @@
         <v>16</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>200</v>
@@ -4955,7 +4950,7 @@
         <v>16</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>200</v>
@@ -4979,7 +4974,7 @@
         <v>16</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>200</v>
@@ -5003,7 +4998,7 @@
         <v>16</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>91</v>
@@ -5027,7 +5022,7 @@
         <v>16</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>91</v>
@@ -5036,7 +5031,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>260</v>
@@ -5051,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>91</v>
@@ -5071,8 +5066,8 @@
       <c r="D77" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="E77" s="10" t="s">
-        <v>867</v>
+      <c r="E77" s="13">
+        <v>18300000000</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>264</v>
@@ -5336,7 +5331,7 @@
         <v>296</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>277</v>
@@ -5623,8 +5618,8 @@
       <c r="D100" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="E100" s="10" t="s">
-        <v>868</v>
+      <c r="E100" s="10">
+        <v>815000000</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>277</v>
@@ -5648,7 +5643,7 @@
         <v>333</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>277</v>
@@ -5672,7 +5667,7 @@
         <v>336</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>277</v>
@@ -5708,19 +5703,19 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>277</v>
@@ -5729,21 +5724,21 @@
         <v>305</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>16</v>
@@ -5755,7 +5750,7 @@
         <v>305</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
   </sheetData>
@@ -5803,7 +5798,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5823,7 +5818,7 @@
         <v>346</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
@@ -5847,7 +5842,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>12</v>
@@ -5871,7 +5866,7 @@
         <v>352</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>12</v>
@@ -5895,7 +5890,7 @@
         <v>355</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>12</v>
@@ -5919,7 +5914,7 @@
         <v>359</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>12</v>
@@ -5943,7 +5938,7 @@
         <v>362</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>12</v>
@@ -5967,7 +5962,7 @@
         <v>365</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>12</v>
@@ -5991,7 +5986,7 @@
         <v>368</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>12</v>
@@ -6015,7 +6010,7 @@
         <v>371</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>12</v>
@@ -6039,7 +6034,7 @@
         <v>374</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>12</v>
@@ -6063,7 +6058,7 @@
         <v>377</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>12</v>
@@ -6087,7 +6082,7 @@
         <v>380</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>12</v>
@@ -6111,7 +6106,7 @@
         <v>383</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>12</v>
@@ -6135,7 +6130,7 @@
         <v>386</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>12</v>
@@ -6159,7 +6154,7 @@
         <v>389</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>12</v>
@@ -6183,7 +6178,7 @@
         <v>392</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>12</v>
@@ -6207,7 +6202,7 @@
         <v>395</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>12</v>
@@ -6231,7 +6226,7 @@
         <v>398</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>59</v>
@@ -6255,7 +6250,7 @@
         <v>401</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>59</v>
@@ -6279,7 +6274,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>59</v>
@@ -6303,7 +6298,7 @@
         <v>406</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>59</v>
@@ -6327,7 +6322,7 @@
         <v>16</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>59</v>
@@ -6351,7 +6346,7 @@
         <v>411</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>59</v>
@@ -6375,7 +6370,7 @@
         <v>414</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>59</v>
@@ -6399,7 +6394,7 @@
         <v>16</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>59</v>
@@ -6423,7 +6418,7 @@
         <v>419</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>59</v>
@@ -6447,7 +6442,7 @@
         <v>421</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>59</v>
@@ -6471,7 +6466,7 @@
         <v>424</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>59</v>
@@ -6495,7 +6490,7 @@
         <v>427</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>59</v>
@@ -6519,7 +6514,7 @@
         <v>430</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>59</v>
@@ -6543,7 +6538,7 @@
         <v>433</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>59</v>
@@ -6567,7 +6562,7 @@
         <v>436</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>59</v>
@@ -6591,7 +6586,7 @@
         <v>439</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>59</v>
@@ -6615,7 +6610,7 @@
         <v>442</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>59</v>
@@ -6639,7 +6634,7 @@
         <v>445</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>59</v>
@@ -6663,7 +6658,7 @@
         <v>448</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>59</v>
@@ -6687,7 +6682,7 @@
         <v>451</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>59</v>
@@ -6711,7 +6706,7 @@
         <v>454</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>59</v>
@@ -6735,7 +6730,7 @@
         <v>457</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>91</v>
@@ -6759,7 +6754,7 @@
         <v>460</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>91</v>
@@ -6783,7 +6778,7 @@
         <v>88</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>91</v>
@@ -6807,7 +6802,7 @@
         <v>465</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>91</v>
@@ -6831,7 +6826,7 @@
         <v>468</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>91</v>
@@ -6855,7 +6850,7 @@
         <v>471</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>91</v>
@@ -6879,7 +6874,7 @@
         <v>474</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>91</v>
@@ -6903,7 +6898,7 @@
         <v>477</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>91</v>
@@ -6927,7 +6922,7 @@
         <v>480</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>91</v>
@@ -6951,7 +6946,7 @@
         <v>483</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>91</v>
@@ -6975,7 +6970,7 @@
         <v>486</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>91</v>
@@ -6999,7 +6994,7 @@
         <v>489</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>91</v>
@@ -7023,7 +7018,7 @@
         <v>492</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>91</v>
@@ -7047,7 +7042,7 @@
         <v>495</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>91</v>
@@ -7071,7 +7066,7 @@
         <v>498</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>91</v>
@@ -7095,7 +7090,7 @@
         <v>501</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>91</v>
@@ -7119,7 +7114,7 @@
         <v>504</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>91</v>
@@ -7143,7 +7138,7 @@
         <v>507</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>91</v>
@@ -7167,7 +7162,7 @@
         <v>510</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>91</v>
@@ -7191,7 +7186,7 @@
         <v>16</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>91</v>
@@ -7215,7 +7210,7 @@
         <v>515</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>91</v>
@@ -7239,7 +7234,7 @@
         <v>518</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>123</v>
@@ -7263,7 +7258,7 @@
         <v>521</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>123</v>
@@ -7287,7 +7282,7 @@
         <v>524</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>123</v>
@@ -7311,7 +7306,7 @@
         <v>527</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>123</v>
@@ -7335,7 +7330,7 @@
         <v>530</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>123</v>
@@ -7359,7 +7354,7 @@
         <v>533</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>123</v>
@@ -7383,7 +7378,7 @@
         <v>536</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>123</v>
@@ -7407,7 +7402,7 @@
         <v>539</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>123</v>
@@ -7431,7 +7426,7 @@
         <v>542</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>123</v>
@@ -7455,7 +7450,7 @@
         <v>545</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>123</v>
@@ -7479,7 +7474,7 @@
         <v>548</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>123</v>
@@ -7503,7 +7498,7 @@
         <v>551</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>123</v>
@@ -7527,7 +7522,7 @@
         <v>554</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>123</v>
@@ -7551,7 +7546,7 @@
         <v>557</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>123</v>
@@ -7575,7 +7570,7 @@
         <v>560</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>123</v>
@@ -7599,7 +7594,7 @@
         <v>563</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>123</v>
@@ -7623,7 +7618,7 @@
         <v>566</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>123</v>
@@ -7647,7 +7642,7 @@
         <v>569</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>123</v>
@@ -7671,7 +7666,7 @@
         <v>572</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>123</v>
@@ -7695,7 +7690,7 @@
         <v>575</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>123</v>
@@ -7719,7 +7714,7 @@
         <v>578</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>123</v>
@@ -7743,7 +7738,7 @@
         <v>581</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>123</v>
@@ -7767,7 +7762,7 @@
         <v>584</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>123</v>
@@ -7791,7 +7786,7 @@
         <v>587</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>123</v>
@@ -7815,7 +7810,7 @@
         <v>590</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>123</v>
@@ -7839,7 +7834,7 @@
         <v>593</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>123</v>
@@ -7863,7 +7858,7 @@
         <v>596</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>123</v>
@@ -7887,7 +7882,7 @@
         <v>16</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>163</v>
@@ -7911,7 +7906,7 @@
         <v>601</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>163</v>
@@ -7935,7 +7930,7 @@
         <v>604</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>163</v>
@@ -7959,7 +7954,7 @@
         <v>607</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>163</v>
@@ -7983,7 +7978,7 @@
         <v>610</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>163</v>
@@ -8007,7 +8002,7 @@
         <v>612</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>163</v>
@@ -8031,7 +8026,7 @@
         <v>615</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>163</v>
@@ -8055,7 +8050,7 @@
         <v>618</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>163</v>
@@ -8079,7 +8074,7 @@
         <v>621</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>163</v>
@@ -8103,7 +8098,7 @@
         <v>624</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>163</v>
@@ -8127,7 +8122,7 @@
         <v>627</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>163</v>
@@ -8151,7 +8146,7 @@
         <v>630</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>163</v>
@@ -8175,7 +8170,7 @@
         <v>633</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>163</v>
@@ -8199,7 +8194,7 @@
         <v>16</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>163</v>
@@ -8223,7 +8218,7 @@
         <v>638</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>163</v>
@@ -8247,7 +8242,7 @@
         <v>641</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>163</v>
@@ -8271,7 +8266,7 @@
         <v>644</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>200</v>
@@ -8295,7 +8290,7 @@
         <v>647</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>200</v>
@@ -8319,7 +8314,7 @@
         <v>650</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>200</v>
@@ -8343,7 +8338,7 @@
         <v>653</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>200</v>
@@ -8367,7 +8362,7 @@
         <v>656</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>200</v>
@@ -8391,7 +8386,7 @@
         <v>659</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>200</v>
@@ -8415,7 +8410,7 @@
         <v>662</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>200</v>
@@ -8439,7 +8434,7 @@
         <v>665</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>200</v>
@@ -8463,7 +8458,7 @@
         <v>668</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>200</v>
@@ -8487,7 +8482,7 @@
         <v>16</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>200</v>
@@ -8511,7 +8506,7 @@
         <v>673</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>200</v>
@@ -8535,7 +8530,7 @@
         <v>676</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>200</v>
@@ -8559,7 +8554,7 @@
         <v>16</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>200</v>
@@ -8583,7 +8578,7 @@
         <v>681</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>200</v>
@@ -8607,7 +8602,7 @@
         <v>684</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>200</v>
@@ -10176,13 +10171,13 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>344</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D184" s="12">
         <v>4500000</v>
@@ -10197,7 +10192,7 @@
         <v>231</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -10208,7 +10203,7 @@
         <v>344</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="D185" s="12">
         <v>7500000</v>
@@ -10217,39 +10212,39 @@
         <v>16</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>200</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>344</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D186" s="12">
         <v>2000000</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -10260,13 +10255,13 @@
         <v>344</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D187" s="12">
         <v>11600000</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>277</v>
@@ -10275,7 +10270,7 @@
         <v>231</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -10286,7 +10281,7 @@
         <v>344</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D188" s="12">
         <v>29400000</v>
@@ -10295,24 +10290,24 @@
         <v>16</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>200</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>344</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D189" s="12">
         <v>3000000</v>
@@ -10321,13 +10316,13 @@
         <v>16</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>163</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
   </sheetData>
@@ -10354,36 +10349,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>881</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>883</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>872</v>
+      </c>
+      <c r="B2" t="s">
+        <v>873</v>
+      </c>
+      <c r="C2" t="s">
         <v>874</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>875</v>
-      </c>
-      <c r="C2" t="s">
-        <v>876</v>
-      </c>
-      <c r="D2" t="s">
-        <v>877</v>
       </c>
       <c r="E2" s="3">
         <v>17000000</v>
@@ -10400,13 +10395,13 @@
         <v>466</v>
       </c>
       <c r="B3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C3" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="D3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E3" s="3">
         <v>75000000</v>
@@ -10420,22 +10415,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>904</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>875</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>905</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>906</v>
-      </c>
       <c r="E4" s="7" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G4" s="6">
         <v>45658</v>
@@ -10443,22 +10438,22 @@
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G5" s="6">
         <v>45717</v>
@@ -10466,22 +10461,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G6" s="6">
         <v>45809</v>
@@ -10492,16 +10487,16 @@
         <v>717</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>277</v>
@@ -10512,19 +10507,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>277</v>
@@ -10538,16 +10533,16 @@
         <v>816</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>277</v>
